--- a/src/attributions/attributions_saliency_traj_450.xlsx
+++ b/src/attributions/attributions_saliency_traj_450.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1874334812164307</v>
+        <v>0.01193100586533546</v>
       </c>
       <c r="B3" t="n">
-        <v>1.174167037010193</v>
+        <v>0.01177006214857101</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1366700232028961</v>
+        <v>0.0002966588363051414</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3157332837581635</v>
+        <v>0.00339774414896965</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2932968139648438</v>
+        <v>0.003915684297680855</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1372039467096329</v>
+        <v>0.006618381012231112</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005135741084814072</v>
+        <v>0.005196457728743553</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00472415704280138</v>
+        <v>0.0008348121773451567</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06461440026760101</v>
+        <v>0.004790719132870436</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2934383451938629</v>
+        <v>0.009858175180852413</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9972403049468994</v>
+        <v>0.02215925976634026</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05488663166761398</v>
+        <v>0.0009202311048284173</v>
       </c>
       <c r="M3" t="n">
-        <v>0.49472975730896</v>
+        <v>0.01050910726189613</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3808223605155945</v>
+        <v>1.932866871356964e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1730814725160599</v>
+        <v>0.007226342335343361</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01006568223237991</v>
+        <v>0.00272437441162765</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1696846038103104</v>
+        <v>0.01003118604421616</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1518992632627487</v>
+        <v>0.001539587043225765</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05171718820929527</v>
+        <v>0.001418218715116382</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2376505583524704</v>
+        <v>0.002222917275503278</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01135065220296383</v>
+        <v>0.002495771972462535</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07492361962795258</v>
+        <v>0.002222038339823484</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1777337789535522</v>
+        <v>0.000410764361731708</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1000659689307213</v>
+        <v>0.00141855888068676</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02873995900154114</v>
+        <v>0.0005622737226076424</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.135853499174118</v>
+        <v>0.00194653938524425</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08560037612915039</v>
+        <v>0.003229294903576374</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1146728545427322</v>
+        <v>0.001616004039533436</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.172933503985405</v>
+        <v>4.340238228905946e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1044709607958794</v>
+        <v>0.002853578189387918</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09225244075059891</v>
+        <v>0.006030429154634476</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1495141535997391</v>
+        <v>0.0005441959947347641</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.09808097779750824</v>
+        <v>0.003587240818887949</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02289428375661373</v>
+        <v>0.002009427174925804</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0003624577075242996</v>
+        <v>0.004807295277714729</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0144845824688673</v>
+        <v>0.001120111322961748</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.110375888645649</v>
+        <v>0.001187070505693555</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1451651453971863</v>
+        <v>0.004284530878067017</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.02576176077127457</v>
+        <v>0.001517894910648465</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0625445693731308</v>
+        <v>0.0009356671944260597</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08440963923931122</v>
+        <v>0.004909716546535492</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1506190001964569</v>
+        <v>0.002161410171538591</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.01546703092753887</v>
+        <v>0.000949017470702529</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.003534838557243347</v>
+        <v>0.005728666670620441</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.07143621146678925</v>
+        <v>0.0001381550682708621</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.008420359343290329</v>
+        <v>0.002221369650214911</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.6640658974647522</v>
+        <v>0.01544507034122944</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.08558817207813263</v>
+        <v>0.001538099255412817</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.145680844783783</v>
+        <v>0.009805666282773018</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1668777912855148</v>
+        <v>0.00280281831510365</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.088369220495224</v>
+        <v>0.001423336565494537</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2004780918359756</v>
+        <v>0.0005512949428521097</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.001935243606567383</v>
+        <v>0.0009206924005411565</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.03903328254818916</v>
+        <v>0.002283287001773715</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.02366500347852707</v>
+        <v>0.007107722107321024</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.203141376376152</v>
+        <v>0.005341673269867897</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1827467232942581</v>
+        <v>0.00175061565823853</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1404949277639389</v>
+        <v>0.002649592934176326</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.2828280031681061</v>
+        <v>0.002896300284191966</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.06684321910142899</v>
+        <v>0.003116962965577841</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1123082041740417</v>
+        <v>0.0005162244196981192</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.09428386390209198</v>
+        <v>0.00151820934843272</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.08800670504570007</v>
+        <v>0.007102052215486765</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.009112495929002762</v>
+        <v>0.001804900821298361</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.04636141285300255</v>
+        <v>0.00237928656861186</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.05128166824579239</v>
+        <v>0.001646490767598152</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.04411576315760612</v>
+        <v>0.001552165835164487</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1694181859493256</v>
+        <v>0.0008567477343603969</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1189005225896835</v>
+        <v>0.001992912264540792</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.08192227780818939</v>
+        <v>0.006381948478519917</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.09695643186569214</v>
+        <v>0.0006831716746091843</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1332598775625229</v>
+        <v>0.0002949726185761392</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.03803753107786179</v>
+        <v>1.627733581699431e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.3647027611732483</v>
+        <v>0.01218920946121216</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1442281603813171</v>
+        <v>0.002610464347526431</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.03307642415165901</v>
+        <v>0.008281118236482143</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.09381276369094849</v>
+        <v>0.002667107386514544</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.003650225233286619</v>
+        <v>0.002384466584771872</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0628262385725975</v>
+        <v>0.003236644901335239</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.03532319143414497</v>
+        <v>0.0003956368891522288</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.07401256263256073</v>
+        <v>0.002468856750056148</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.02001530863344669</v>
+        <v>0.001418194849975407</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.2151750922203064</v>
+        <v>0.004900975618511438</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.04489206895232201</v>
+        <v>0.0007911158609203994</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.02617873623967171</v>
+        <v>0.0006853397935628891</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.00646558590233326</v>
+        <v>0.002655538264662027</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01783866062760353</v>
+        <v>0.0008435843628831208</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.04201002418994904</v>
+        <v>0.0007785975467413664</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.01830406673252583</v>
+        <v>0.0005419786320999265</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.001053368672728539</v>
+        <v>0.002011570148169994</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.2104822844266891</v>
+        <v>0.003195907920598984</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.06361887603998184</v>
+        <v>0.009984397329390049</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.05763035640120506</v>
+        <v>0.00134467741008848</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.2071806639432907</v>
+        <v>0.009959658607840538</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.2781183123588562</v>
+        <v>0.00473257340490818</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1158445104956627</v>
+        <v>0.0001872709253802896</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1442816704511642</v>
+        <v>0.003098670626059175</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1335178464651108</v>
+        <v>0.001264214282855392</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.02082039788365364</v>
+        <v>0.004470066167414188</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.005940065253525972</v>
+        <v>0.0002912896743509918</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2171172499656677</v>
+        <v>0.004930224269628525</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0639120414853096</v>
+        <v>0.0003105717769358307</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.06823620200157166</v>
+        <v>0.0015806540613994</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.009816945530474186</v>
+        <v>0.00452131126075983</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.002062613610178232</v>
+        <v>0.0006057777209207416</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.07504911720752716</v>
+        <v>0.0003213630407117307</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.02781382203102112</v>
+        <v>9.136946755461395e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0003633499145507812</v>
+        <v>0.002365631982684135</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06474673002958298</v>
+        <v>0.0001975265186047181</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.3168402314186096</v>
+        <v>0.01278028823435307</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.06540004163980484</v>
+        <v>0.001720728119835258</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.03395636007189751</v>
+        <v>0.0007441974012181163</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02504998259246349</v>
+        <v>0.0001212223432958126</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.007496174424886703</v>
+        <v>0.004824920557439327</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.04778341948986053</v>
+        <v>0.00212102965451777</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07995077967643738</v>
+        <v>0.005677697248756886</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.003943442367017269</v>
+        <v>0.003530028508976102</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.06363321095705032</v>
+        <v>0.0005465378053486347</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.1396892666816711</v>
+        <v>0.0004923069500364363</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.0528244860470295</v>
+        <v>0.0002761412179097533</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1214384809136391</v>
+        <v>0.003412733087316155</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1042631864547729</v>
+        <v>0.003662346163764596</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.02151685580611229</v>
+        <v>0.0005327758262865245</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07593436539173126</v>
+        <v>0.001428148243576288</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.02704517915844917</v>
+        <v>0.001265647122636437</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.02798672020435333</v>
+        <v>0.003533715847879648</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.003951992839574814</v>
+        <v>0.002388450084254146</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2119205296039581</v>
+        <v>0.006819067988544703</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0194092895835638</v>
+        <v>0.002943458268418908</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.09820406883955002</v>
+        <v>0.004412917420268059</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.05455410107970238</v>
+        <v>8.331132994499058e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.09031199663877487</v>
+        <v>0.003193603130057454</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01184107922017574</v>
+        <v>0.002194928470999002</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.1560710668563843</v>
+        <v>0.00317739206366241</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.03834106773138046</v>
+        <v>0.006862047128379345</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.01039377227425575</v>
+        <v>1.71374122146517e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.09913843125104904</v>
+        <v>0.0002950665075331926</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.04579013958573341</v>
+        <v>0.0003860622528009117</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.02092143520712852</v>
+        <v>0.0004497743211686611</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.05852336809039116</v>
+        <v>0.004028772935271263</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0227978304028511</v>
+        <v>0.0006782007403671741</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.105936661362648</v>
+        <v>0.0002176070120185614</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.02357893064618111</v>
+        <v>0.0005786995170637965</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.03630084544420242</v>
+        <v>0.001267016399651766</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.01225440204143524</v>
+        <v>0.0002728488179855049</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.186582013964653</v>
+        <v>0.004103119485080242</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.1285841315984726</v>
+        <v>0.001797828124836087</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.06696166098117828</v>
+        <v>0.000725754420273006</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03320393711328506</v>
+        <v>0.0001321492018178105</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.02270646020770073</v>
+        <v>0.003663917537778616</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.04686909541487694</v>
+        <v>0.001797888893634081</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.06324481964111328</v>
+        <v>0.002305948175489902</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.03390850499272346</v>
+        <v>0.002213943982496858</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02319303527474403</v>
+        <v>0.0006751244654878974</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2281766980886459</v>
+        <v>0.006835442036390305</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.03525438532233238</v>
+        <v>7.011689012870193e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.02414577081799507</v>
+        <v>0.001421549590304494</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02617188356816769</v>
+        <v>0.004385501611977816</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.0111882109194994</v>
+        <v>0.0002254362334497273</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.07858432829380035</v>
+        <v>0.0006994361756369472</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.03799222037196159</v>
+        <v>0.000584275578148663</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.02351614832878113</v>
+        <v>0.002323694759979844</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01569171436131001</v>
+        <v>0.0007189275929704309</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.02743617817759514</v>
+        <v>0.003129377262666821</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.08185573667287827</v>
+        <v>0.002514165593311191</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.08068058639764786</v>
+        <v>0.002758647780865431</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.09133830666542053</v>
+        <v>0.003966887481510639</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.03898730501532555</v>
+        <v>0.003323856042698026</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.08364098519086838</v>
+        <v>6.511269748443738e-05</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.0544421449303627</v>
+        <v>0.003414055332541466</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.02110466919839382</v>
+        <v>0.001362768816761672</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06866534054279327</v>
+        <v>0.004180433694273233</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2011135369539261</v>
+        <v>0.00118572951760143</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.1161793693900108</v>
+        <v>0.0004081104998476803</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.05393354967236519</v>
+        <v>0.004912427626550198</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.06905032694339752</v>
+        <v>0.007080125156790018</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.05022833868861198</v>
+        <v>0.003046086058020592</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.0437638908624649</v>
+        <v>0.001375080551952124</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2444706857204437</v>
+        <v>0.0009000446880236268</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.003263190388679504</v>
+        <v>0.003719552187249064</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.1513832360506058</v>
+        <v>0.003128516487777233</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.02175978571176529</v>
+        <v>0.002024258719757199</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.003448285162448883</v>
+        <v>0.0003468695795163512</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.05747028812766075</v>
+        <v>0.0009488787036389112</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.2668677568435669</v>
+        <v>0.007713957224041224</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1271781623363495</v>
+        <v>0.001577347284182906</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.2231973558664322</v>
+        <v>0.004410205874592066</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.1033066511154175</v>
+        <v>0.0005650535458698869</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.01454924233257771</v>
+        <v>0.0002104765007970855</v>
       </c>
     </row>
     <row r="4">
@@ -2706,5123 +2706,5123 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8.706687367521226e-05</v>
+        <v>0.04663437232375145</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00301927444525063</v>
+        <v>0.2112460434436798</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002099820121657103</v>
+        <v>0.03671827539801598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001249439781531692</v>
+        <v>0.1688433438539505</v>
       </c>
       <c r="E5" t="n">
-        <v>1.772912219166756e-05</v>
+        <v>0.09491440653800964</v>
       </c>
       <c r="F5" t="n">
-        <v>5.676033833879046e-05</v>
+        <v>0.07923758029937744</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004008414398413152</v>
+        <v>0.0588703453540802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001121189794503152</v>
+        <v>0.08922529220581055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001237065152963623</v>
+        <v>0.01226067449897528</v>
       </c>
       <c r="J5" t="n">
-        <v>8.025672286748886e-07</v>
+        <v>0.01223520375788212</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002658883575350046</v>
+        <v>0.2363684475421906</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000117341274744831</v>
+        <v>0.002689626067876816</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001645230338908732</v>
+        <v>0.2327477186918259</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004555725608952343</v>
+        <v>0.1269180923700333</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006383443251252174</v>
+        <v>0.07822836190462112</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002529897610656917</v>
+        <v>0.0820733830332756</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0004422509227879345</v>
+        <v>0.008130433037877083</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001966504351003096</v>
+        <v>0.02640151791274548</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001381563197355717</v>
+        <v>0.0151565158739686</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007326180348172784</v>
+        <v>0.01621167734265327</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0002237341104773805</v>
+        <v>0.01956626027822495</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001672255166340619</v>
+        <v>0.006551619619131088</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0008211043896153569</v>
+        <v>0.04347408562898636</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0004539426299743354</v>
+        <v>0.04527261108160019</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001743646862450987</v>
+        <v>0.00769035192206502</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001476339239161462</v>
+        <v>0.03194072842597961</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001582795666763559</v>
+        <v>0.02797342836856842</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.174348290078342e-05</v>
+        <v>0.007291728630661964</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.000899846781976521</v>
+        <v>0.02622168697416782</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0002188359794672579</v>
+        <v>0.001740902895107865</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0002171360538341105</v>
+        <v>0.04218683764338493</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0002187395730288699</v>
+        <v>0.009143747389316559</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0001623493590159342</v>
+        <v>0.007081302814185619</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0006953779375180602</v>
+        <v>0.001846692524850368</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0003049967053811997</v>
+        <v>0.05993553996086121</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001158785016741604</v>
+        <v>0.00784385297447443</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0001693929953034967</v>
+        <v>0.00010672677308321</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0001678338448982686</v>
+        <v>0.05073273554444313</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.019474257191177e-05</v>
+        <v>0.003573435358703136</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0005094971274957061</v>
+        <v>0.03260229900479317</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0004391305847093463</v>
+        <v>0.004440862685441971</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0001475885510444641</v>
+        <v>0.01548280473798513</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0003446565533522516</v>
+        <v>0.01099227461963892</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0002299441257491708</v>
+        <v>0.03163813799619675</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.030204192735255e-05</v>
+        <v>0.01802924275398254</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0001369229430565611</v>
+        <v>0.01593870297074318</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001917376415804029</v>
+        <v>0.1961508691310883</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0006195041351020336</v>
+        <v>0.03678646311163902</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0003158085455652326</v>
+        <v>0.1137312948703766</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0012212167493999</v>
+        <v>0.1248696148395538</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0003582584904506803</v>
+        <v>0.03123129159212112</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0002826061099767685</v>
+        <v>0.007782714441418648</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.000916133401915431</v>
+        <v>0.00468048732727766</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.000145546582643874</v>
+        <v>0.02272130735218525</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0006859867135062814</v>
+        <v>0.05809562280774117</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0003930122475139797</v>
+        <v>0.04431090131402016</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.000661688856780529</v>
+        <v>0.02286861836910248</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.234047421254218e-06</v>
+        <v>0.001452061231248081</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0007490813150070608</v>
+        <v>0.00707678496837616</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0001162170228781179</v>
+        <v>0.03286058828234673</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0002021403633989394</v>
+        <v>0.02311025746166706</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0002273080172017217</v>
+        <v>0.05372140556573868</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0001587088336236775</v>
+        <v>0.01485530380159616</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0004789028316736221</v>
+        <v>0.01191804371774197</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0002104432205669582</v>
+        <v>0.05211873725056648</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0001503513485658914</v>
+        <v>0.005384943448007107</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0008721929043531418</v>
+        <v>0.004293709062039852</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.001011211075820029</v>
+        <v>0.02522069215774536</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.000494548468850553</v>
+        <v>0.008431646972894669</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0002792757877614349</v>
+        <v>0.06368096917867661</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.168887193780392e-05</v>
+        <v>0.02599122002720833</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0007190096657723188</v>
+        <v>0.01303412392735481</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.774290624074638e-05</v>
+        <v>0.02474915236234665</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001087044249288738</v>
+        <v>0.128592848777771</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0001577701477799565</v>
+        <v>0.004727037623524666</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0001546146813780069</v>
+        <v>0.09131330251693726</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0007028183317743242</v>
+        <v>0.06390485167503357</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0001493566669523716</v>
+        <v>0.0487026683986187</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.000306129310047254</v>
+        <v>0.02771569229662418</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0002326805988559499</v>
+        <v>0.01283882092684507</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0001159347521024756</v>
+        <v>0.005355722270905972</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.906660175649449e-05</v>
+        <v>0.0014868238940835</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0006542634801007807</v>
+        <v>0.06383698433637619</v>
       </c>
       <c r="CF5" t="n">
-        <v>8.214152330765501e-06</v>
+        <v>0.00600806949660182</v>
       </c>
       <c r="CG5" t="n">
-        <v>1.324007462244481e-05</v>
+        <v>0.05183352902531624</v>
       </c>
       <c r="CH5" t="n">
-        <v>6.469881918746978e-05</v>
+        <v>0.01806389167904854</v>
       </c>
       <c r="CI5" t="n">
-        <v>6.00492894591298e-05</v>
+        <v>0.009131500497460365</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0001293038803851232</v>
+        <v>0.02058524638414383</v>
       </c>
       <c r="CK5" t="n">
-        <v>4.909978088107891e-05</v>
+        <v>0.01292701810598373</v>
       </c>
       <c r="CL5" t="n">
-        <v>7.316227129194885e-05</v>
+        <v>0.004552105907350779</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0007106829434633255</v>
+        <v>0.02047511003911495</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004166384169366211</v>
+        <v>0.1639354825019836</v>
       </c>
       <c r="CO5" t="n">
-        <v>9.363787830807269e-05</v>
+        <v>0.05711213499307632</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.00115254835691303</v>
+        <v>0.103596068918705</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0008719873148947954</v>
+        <v>0.01461469009518623</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001061496557667851</v>
+        <v>0.01096065901219845</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.00028749875491485</v>
+        <v>0.02225116640329361</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0005321434000506997</v>
+        <v>0.03871854394674301</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0001943256938830018</v>
+        <v>0.00307424133643508</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0001071423321263865</v>
+        <v>0.005321229808032513</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0005674536805599928</v>
+        <v>0.06126032024621964</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0001668680924922228</v>
+        <v>0.005013332702219486</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0001967638818314299</v>
+        <v>0.06422996520996094</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001580189127707854</v>
+        <v>0.005006072111427784</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.815599691530224e-05</v>
+        <v>0.006156312301754951</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001521031517768279</v>
+        <v>0.01767350174486637</v>
       </c>
       <c r="DC5" t="n">
-        <v>7.324963371502236e-05</v>
+        <v>0.01048876624554396</v>
       </c>
       <c r="DD5" t="n">
-        <v>6.61355588817969e-05</v>
+        <v>0.008541922084987164</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0003032284439541399</v>
+        <v>0.04011359065771103</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0006006977637298405</v>
+        <v>0.08042596280574799</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0001436808088328689</v>
+        <v>0.03233529254794121</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0003622088115662336</v>
+        <v>0.05886808782815933</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0009102382464334369</v>
+        <v>0.01715792343020439</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0001541778619866818</v>
+        <v>0.04197040200233459</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0001868671388365328</v>
+        <v>0.004057944286614656</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0001326769561273977</v>
+        <v>0.07973536849021912</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0001188603055197746</v>
+        <v>0.0179752055555582</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0002096493117278442</v>
+        <v>0.03166793286800385</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003757273661904037</v>
+        <v>0.01556720957159996</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0002485853619873524</v>
+        <v>0.002527415752410889</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0006855422980152071</v>
+        <v>0.0002007381990551949</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0005198348662815988</v>
+        <v>0.01424700114876032</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.000126073049614206</v>
+        <v>0.01952489279210567</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001942039525602013</v>
+        <v>0.01199768111109734</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0001153352350229397</v>
+        <v>0.03068799152970314</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0005613936227746308</v>
+        <v>0.04939696192741394</v>
       </c>
       <c r="DW5" t="n">
-        <v>2.661212056409568e-05</v>
+        <v>0.02795359119772911</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0002601345186121762</v>
+        <v>0.002460493240505457</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0002488727914169431</v>
+        <v>0.01382740400731564</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002133293310180306</v>
+        <v>0.05909918248653412</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.845648512244225e-06</v>
+        <v>0.02323084883391857</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0001292741508223116</v>
+        <v>0.01471632346510887</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0001594794739503413</v>
+        <v>0.003887824947014451</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0005070181214250624</v>
+        <v>0.07154984027147293</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0001507672277512029</v>
+        <v>0.04224585369229317</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.000126733270008117</v>
+        <v>0.0399509072303772</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0003492774849291891</v>
+        <v>0.03880221024155617</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0002170399093301967</v>
+        <v>0.003095818683505058</v>
       </c>
       <c r="EI5" t="n">
-        <v>4.248414188623428e-05</v>
+        <v>0.04362104088068008</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0006888650823384523</v>
+        <v>0.01486023515462875</v>
       </c>
       <c r="EK5" t="n">
-        <v>5.827882341691293e-05</v>
+        <v>0.007524681277573109</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0001616989902686328</v>
+        <v>0.01190807390958071</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0001416397280991077</v>
+        <v>0.01247749477624893</v>
       </c>
       <c r="EN5" t="n">
-        <v>7.083600212354213e-05</v>
+        <v>0.003943684976547956</v>
       </c>
       <c r="EO5" t="n">
-        <v>8.933748176787049e-05</v>
+        <v>0.005886630155146122</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0005964258452877402</v>
+        <v>0.06024759262800217</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0002553644881118089</v>
+        <v>0.01980421133339405</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0007557932985946536</v>
+        <v>0.0100442161783576</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0002917294041253626</v>
+        <v>0.01333128660917282</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.000194850261323154</v>
+        <v>0.005189755465835333</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0001442558568669483</v>
+        <v>0.0333053357899189</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0004103020473849028</v>
+        <v>0.02083056420087814</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001578950032126158</v>
+        <v>0.03781348839402199</v>
       </c>
       <c r="EX5" t="n">
-        <v>9.131665137829259e-06</v>
+        <v>0.004078423604369164</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0006368097383528948</v>
+        <v>0.0763033926486969</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.999064574600197e-05</v>
+        <v>0.0005389396101236343</v>
       </c>
       <c r="FA5" t="n">
-        <v>4.80505550513044e-05</v>
+        <v>0.06628605723381042</v>
       </c>
       <c r="FB5" t="n">
-        <v>9.054614929482341e-05</v>
+        <v>0.004861973691731691</v>
       </c>
       <c r="FC5" t="n">
-        <v>2.616855999804102e-05</v>
+        <v>0.008057164959609509</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0001112509416998364</v>
+        <v>0.02288513071835041</v>
       </c>
       <c r="FE5" t="n">
-        <v>5.690547186532058e-05</v>
+        <v>0.02597220242023468</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.000133852765429765</v>
+        <v>0.008898751810193062</v>
       </c>
       <c r="FG5" t="n">
-        <v>9.55099385464564e-05</v>
+        <v>0.03293606266379356</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0001084342802641913</v>
+        <v>0.04247111454606056</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0005805406835861504</v>
+        <v>0.01656259968876839</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0002357877674512565</v>
+        <v>0.05872733518481255</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0002802334784064442</v>
+        <v>0.009858414530754089</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0002440566750010476</v>
+        <v>0.001008103135973215</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0001454620505683124</v>
+        <v>0.01664374768733978</v>
       </c>
       <c r="FN5" t="n">
-        <v>5.680692993337288e-05</v>
+        <v>0.004208192229270935</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0003156644816044718</v>
+        <v>0.009216018952429295</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0002335105382371694</v>
+        <v>0.02992661669850349</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001533122849650681</v>
+        <v>0.08001308143138885</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0004323612956795841</v>
+        <v>0.04615370556712151</v>
       </c>
       <c r="FS5" t="n">
-        <v>7.709278725087643e-05</v>
+        <v>0.08493613451719284</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0001443930668756366</v>
+        <v>0.1832954883575439</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001196069206343964</v>
+        <v>0.03989087417721748</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0005680879112333059</v>
+        <v>0.01226695161312819</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0003842441365122795</v>
+        <v>0.001009475556202233</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0001799307210603729</v>
+        <v>0.07722188532352448</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0003791265480685979</v>
+        <v>0.0186575036495924</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0001349178492091596</v>
+        <v>0.0009051058441400528</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.000144232326420024</v>
+        <v>0.007817806676030159</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0002289889962412417</v>
+        <v>0.003419158980250359</v>
       </c>
       <c r="GC5" t="n">
-        <v>6.018086787662469e-05</v>
+        <v>0.03193029016256332</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0005643132608383894</v>
+        <v>0.01598937436938286</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0008362866356037557</v>
+        <v>0.04820956289768219</v>
       </c>
       <c r="GF5" t="n">
-        <v>6.615524762310088e-05</v>
+        <v>0.03092009201645851</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0002604167093522847</v>
+        <v>0.00208951928652823</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.101574182510376</v>
+        <v>9.107546929953969e-07</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2861509025096893</v>
+        <v>4.262939000909682e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00777813233435154</v>
+        <v>9.89192471934075e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04312169551849365</v>
+        <v>1.00427291727101e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04616162925958633</v>
+        <v>1.798082394088851e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01792985014617443</v>
+        <v>9.837926882028114e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05105390027165413</v>
+        <v>5.265098934614798e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03753090649843216</v>
+        <v>1.562796398957289e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01273811049759388</v>
+        <v>4.675944182963576e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09339240938425064</v>
+        <v>3.381018984782713e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>0.240458220243454</v>
+        <v>5.688320925401058e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01718949899077415</v>
+        <v>1.007351897897024e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1057008802890778</v>
+        <v>1.529195742477896e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08266192674636841</v>
+        <v>2.217431529061287e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03767954558134079</v>
+        <v>2.963855934012827e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05574293062090874</v>
+        <v>5.851782134413952e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05583303794264793</v>
+        <v>1.133417072196607e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0109510151669383</v>
+        <v>5.762174168921774e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00872361846268177</v>
+        <v>2.186710901241895e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07814550399780273</v>
+        <v>6.942511845409172e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00945141538977623</v>
+        <v>1.944961667277312e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01951509527862072</v>
+        <v>3.866840074806532e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>0.043027114123106</v>
+        <v>4.259282704310863e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04202414304018021</v>
+        <v>1.606950519317252e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02663620188832283</v>
+        <v>7.36850722660165e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0112055940553546</v>
+        <v>3.579174290280207e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007489084731787443</v>
+        <v>4.11712562708999e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.071088045835495</v>
+        <v>2.167198118740998e-07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.106446661055088</v>
+        <v>8.8215998061969e-08</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.02590586617588997</v>
+        <v>8.216641163016902e-07</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.03149837628006935</v>
+        <v>4.006870142347907e-07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.005534244701266289</v>
+        <v>4.08328055812035e-08</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003629574552178383</v>
+        <v>2.691697318368824e-07</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.06857868283987045</v>
+        <v>2.208428213634761e-07</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.562579751014709e-06</v>
+        <v>8.638255621917779e-07</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01591534726321697</v>
+        <v>3.872234799473517e-07</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.003820633050054312</v>
+        <v>5.636794142560575e-08</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.05545841157436371</v>
+        <v>1.285977759835077e-06</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.009094040840864182</v>
+        <v>6.270376218253659e-08</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.02961364947259426</v>
+        <v>1.752744935856754e-07</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.006465631071478128</v>
+        <v>8.355975751328515e-07</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.03481484204530716</v>
+        <v>4.436249128048075e-07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01933549903333187</v>
+        <v>2.266194627509321e-07</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.004640771076083183</v>
+        <v>4.381676035336568e-07</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.02830061502754688</v>
+        <v>9.196788397503042e-08</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.001194097800180316</v>
+        <v>3.101404502103833e-07</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1597684174776077</v>
+        <v>3.780989800361567e-06</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.03485792875289917</v>
+        <v>6.723798833263572e-07</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.00452219694852829</v>
+        <v>3.351910891069565e-07</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.03554753214120865</v>
+        <v>7.778045301165548e-07</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.02816266193985939</v>
+        <v>3.121200009559288e-08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.03225649893283844</v>
+        <v>2.167923440765662e-07</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.006102883256971836</v>
+        <v>2.894761053084949e-07</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.02223794162273407</v>
+        <v>1.720607372135419e-07</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.005986536853015423</v>
+        <v>1.033436888064898e-06</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.029914490878582</v>
+        <v>4.878318691226013e-07</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0353788286447525</v>
+        <v>1.27269777294714e-06</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.01429241523146629</v>
+        <v>5.511839162863907e-08</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.09646011888980865</v>
+        <v>7.997788316060905e-07</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.00603719474747777</v>
+        <v>4.05170084150086e-07</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.05968529358506203</v>
+        <v>2.067805837668857e-07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.03578478470444679</v>
+        <v>2.722151464240596e-07</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.003597326809540391</v>
+        <v>1.927811013047176e-07</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.01790656894445419</v>
+        <v>3.012553690950881e-07</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03781400993466377</v>
+        <v>2.082328194319416e-07</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.002004789188504219</v>
+        <v>2.264941940666176e-07</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.006945857778191566</v>
+        <v>6.019037357418711e-08</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01719358749687672</v>
+        <v>7.771116088406416e-07</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.05147143080830574</v>
+        <v>2.66577700358539e-07</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.003054418601095676</v>
+        <v>6.70193514906714e-07</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.03355268016457558</v>
+        <v>1.827006741450532e-07</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.03692629560828209</v>
+        <v>4.158186470704095e-07</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.003626166842877865</v>
+        <v>3.424946157792874e-07</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1238798201084137</v>
+        <v>3.04801824313472e-06</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.039585180580616</v>
+        <v>1.804399119009759e-07</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.001336428336799145</v>
+        <v>5.925659820604778e-07</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.01525431033223867</v>
+        <v>2.812641071159305e-07</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.007430417463183403</v>
+        <v>1.361835018087731e-07</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.009244266897439957</v>
+        <v>3.167172053508693e-07</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.02915899641811848</v>
+        <v>2.077304230851951e-07</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.005790927447378635</v>
+        <v>4.047988113597967e-07</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.01255467720329762</v>
+        <v>6.866617496825711e-08</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.05808752402663231</v>
+        <v>1.441716676708893e-06</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.002578279934823513</v>
+        <v>3.461994992903783e-07</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.001890035346150398</v>
+        <v>1.103407143432378e-08</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.00559705588966608</v>
+        <v>2.55027060802604e-07</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.001826291438192129</v>
+        <v>3.461564119788818e-07</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.01028216630220413</v>
+        <v>2.752222982849162e-08</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.002119134645909071</v>
+        <v>2.836015937646152e-07</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.008423908613622189</v>
+        <v>2.166002843750903e-07</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0727471262216568</v>
+        <v>1.904721216305916e-07</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.02595868334174156</v>
+        <v>2.268743173772236e-06</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0147191034629941</v>
+        <v>5.559207920668996e-07</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0408378541469574</v>
+        <v>4.579496959422613e-08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.03771568462252617</v>
+        <v>2.265316396687922e-07</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.001656918786466122</v>
+        <v>2.314328071406635e-07</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.01251903362572193</v>
+        <v>4.081659312760166e-07</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0004291808581911027</v>
+        <v>6.768395337530819e-07</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.05006537958979607</v>
+        <v>8.061823564275983e-08</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.005998957902193069</v>
+        <v>1.143027148486908e-07</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.06260567158460617</v>
+        <v>1.487396616539627e-06</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.007298570591956377</v>
+        <v>3.406522921522992e-07</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.007292041555047035</v>
+        <v>2.486775088073045e-07</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01601875945925713</v>
+        <v>1.003659235720988e-07</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.007064454257488251</v>
+        <v>3.050109285140934e-07</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0113697461783886</v>
+        <v>1.536520954914522e-07</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.008215215057134628</v>
+        <v>3.216152038021391e-07</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.009836576879024506</v>
+        <v>3.699688591041195e-07</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.01308341696858406</v>
+        <v>2.781381169825181e-07</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.02712382376194</v>
+        <v>1.622143599888659e-06</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.02563155069947243</v>
+        <v>3.50699167483981e-08</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.05974559485912323</v>
+        <v>1.258474213727823e-07</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.002493759617209435</v>
+        <v>1.79524377585949e-08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01865092664957047</v>
+        <v>7.65132767810428e-07</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.009663945063948631</v>
+        <v>6.204621882943684e-08</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.04518567770719528</v>
+        <v>2.718331870710244e-07</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.05298301577568054</v>
+        <v>2.024657703714183e-07</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.008303243666887283</v>
+        <v>2.176449243052048e-08</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.02304958738386631</v>
+        <v>9.625905477150809e-07</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01142842322587967</v>
+        <v>1.051004971941438e-07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0274161733686924</v>
+        <v>1.265466380573343e-07</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.00335036963224411</v>
+        <v>5.710164430183795e-08</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.02756529673933983</v>
+        <v>8.106032112209505e-08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.007949581369757652</v>
+        <v>2.655927460182284e-07</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.01089590694755316</v>
+        <v>5.947033514530631e-07</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.002445879392325878</v>
+        <v>6.395979994522349e-07</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.006530762184411287</v>
+        <v>5.341915993994917e-07</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.03531477227807045</v>
+        <v>1.160590045401477e-06</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.009623910300433636</v>
+        <v>6.156706433557702e-08</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.005300336517393589</v>
+        <v>8.389075389914069e-08</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.006363303400576115</v>
+        <v>4.806639140042535e-07</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.03587381541728973</v>
+        <v>1.17194019821909e-06</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.002918766112998128</v>
+        <v>6.966715204725915e-08</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.05062676966190338</v>
+        <v>2.913245964464295e-07</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.01357827801257372</v>
+        <v>6.1625695479961e-07</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.02694535627961159</v>
+        <v>2.990013854287099e-07</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.03871325775980949</v>
+        <v>6.345646283989481e-07</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.004964366089552641</v>
+        <v>1.082016325426594e-07</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.05186925828456879</v>
+        <v>1.805853315772765e-07</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.005317686591297388</v>
+        <v>1.946719123679941e-07</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01227124407887459</v>
+        <v>5.364261710383289e-07</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.01842348277568817</v>
+        <v>3.756628785822613e-09</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.001790047157555819</v>
+        <v>2.516850940992299e-07</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.01139479130506516</v>
+        <v>1.736924559736508e-07</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.02958108857274055</v>
+        <v>1.659887516325398e-07</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.04800835251808167</v>
+        <v>7.669425485801185e-07</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.02709519676864147</v>
+        <v>3.673581829843897e-07</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.00688711553812027</v>
+        <v>8.425432440617442e-08</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.004219589289277792</v>
+        <v>3.964731831729296e-08</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03139884024858475</v>
+        <v>1.720090665457974e-07</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.003362397197633982</v>
+        <v>7.231916754335543e-08</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.03108076378703117</v>
+        <v>1.264690752122988e-07</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.02232186123728752</v>
+        <v>1.050068973995621e-07</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.002049270551651716</v>
+        <v>4.899091265997413e-08</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.06296012550592422</v>
+        <v>1.649199475650676e-06</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0005291440174914896</v>
+        <v>3.019376322299649e-07</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0009128330275416374</v>
+        <v>8.464749612357991e-08</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.02434143051505089</v>
+        <v>1.131465978687629e-07</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.008921114727854729</v>
+        <v>2.830685730259574e-07</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.001621412113308907</v>
+        <v>6.498275695321354e-09</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.007277967873960733</v>
+        <v>3.194496969172178e-07</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.002358658239245415</v>
+        <v>3.739182545814401e-07</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.003260440193116665</v>
+        <v>3.077695964748273e-07</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01926480233669281</v>
+        <v>5.647062835123506e-07</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0271168015897274</v>
+        <v>4.576478431772557e-07</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.04644247516989708</v>
+        <v>4.411570557749656e-07</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.04257667064666748</v>
+        <v>1.531517739294941e-07</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.006180450785905123</v>
+        <v>4.720305639693834e-07</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.01417742483317852</v>
+        <v>1.982202064709782e-07</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.01121593173593283</v>
+        <v>1.703337062508581e-07</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.001511686481535435</v>
+        <v>8.187979574358906e-07</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.05248468369245529</v>
+        <v>1.166437300526013e-06</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.07586324214935303</v>
+        <v>8.983494126368896e-07</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.02116323821246624</v>
+        <v>5.507683908945182e-07</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.001683479174971581</v>
+        <v>9.517814305581851e-07</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01427676901221275</v>
+        <v>1.086921315618383e-06</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01150594931095839</v>
+        <v>1.238758358113046e-07</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.05314198136329651</v>
+        <v>4.160125115504343e-07</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.03256762772798538</v>
+        <v>9.270791565541003e-07</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.01680975407361984</v>
+        <v>1.022709852804837e-06</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.05919885635375977</v>
+        <v>7.080426200900547e-08</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.005764446221292019</v>
+        <v>9.544936574457097e-07</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.004746520891785622</v>
+        <v>4.129308308620239e-07</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.007577131502330303</v>
+        <v>2.240334850966974e-08</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.09172587096691132</v>
+        <v>2.810268426856055e-07</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.03507358208298683</v>
+        <v>1.489685246269801e-07</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.08247103542089462</v>
+        <v>3.72003626125661e-07</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.02808470278978348</v>
+        <v>2.087054724597692e-07</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.003651824314147234</v>
+        <v>3.491307154490642e-07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.007323970552533865</v>
+        <v>0.2633722424507141</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1230373084545135</v>
+        <v>1.262812495231628</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01062943693250418</v>
+        <v>0.2401717305183411</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08417198061943054</v>
+        <v>1.307297468185425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0397595651447773</v>
+        <v>0.465599536895752</v>
       </c>
       <c r="F7" t="n">
-        <v>0.018618393689394</v>
+        <v>0.3645070791244507</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003742316737771034</v>
+        <v>0.4085680544376373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008184627629816532</v>
+        <v>0.2913450002670288</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002614096272736788</v>
+        <v>0.1105041578412056</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006533656734973192</v>
+        <v>0.5706638693809509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09943896532058716</v>
+        <v>1.159450888633728</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001972294878214598</v>
+        <v>0.2213478684425354</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08241860568523407</v>
+        <v>1.8890540599823</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04758394137024879</v>
+        <v>0.6731606721878052</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01600724086165428</v>
+        <v>0.06077584251761436</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006765889935195446</v>
+        <v>0.3826704025268555</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01745089888572693</v>
+        <v>0.1255131959915161</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01341800764203072</v>
+        <v>0.005459778010845184</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002815149258822203</v>
+        <v>0.04905160516500473</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02578658610582352</v>
+        <v>0.2731232941150665</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01188424788415432</v>
+        <v>0.03272118419408798</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007351367268711329</v>
+        <v>0.03410510346293449</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01563210412859917</v>
+        <v>0.02244068309664726</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0216679684817791</v>
+        <v>0.2211620807647705</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01385937351733446</v>
+        <v>0.01796242967247963</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.004631749354302883</v>
+        <v>0.09855137765407562</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009396336041390896</v>
+        <v>0.1257796734571457</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01160579547286034</v>
+        <v>0.08410099893808365</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01532755605876446</v>
+        <v>0.2009716480970383</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002339910482987761</v>
+        <v>0.05836934596300125</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002447590697556734</v>
+        <v>0.2101179957389832</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.008875366300344467</v>
+        <v>0.0837043821811676</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.004033303819596767</v>
+        <v>0.03842179477214813</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.003915444016456604</v>
+        <v>0.1483060419559479</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.002658416982740164</v>
+        <v>0.05812849476933479</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.005573518574237823</v>
+        <v>0.1597972810268402</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01016436796635389</v>
+        <v>0.0796743631362915</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01348121650516987</v>
+        <v>0.5411379337310791</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.002734004752710462</v>
+        <v>0.006404342129826546</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.007599542383104563</v>
+        <v>0.1127958968281746</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.002927059074863791</v>
+        <v>0.5210934281349182</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01089212577790022</v>
+        <v>0.3628907203674316</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.007851914502680302</v>
+        <v>0.1227123588323593</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01427785307168961</v>
+        <v>0.1756095886230469</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.009122813120484352</v>
+        <v>0.02657690457999706</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01081284414976835</v>
+        <v>0.1127610206604004</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.090210922062397</v>
+        <v>1.028412699699402</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.008034907281398773</v>
+        <v>0.162962481379509</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.02527479268610477</v>
+        <v>0.6236346364021301</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.00129346561152488</v>
+        <v>0.3843920826911926</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.002197400201112032</v>
+        <v>0.0294107049703598</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.00540120480582118</v>
+        <v>0.04232471436262131</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.01501147449016571</v>
+        <v>0.02548645064234734</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.008834574371576309</v>
+        <v>0.314801961183548</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.009793778881430626</v>
+        <v>0.08784988522529602</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01138508506119251</v>
+        <v>0.2343184053897858</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.02275805175304413</v>
+        <v>0.3589849770069122</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.01456582732498646</v>
+        <v>0.01228731498122215</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.03683058544993401</v>
+        <v>0.1936599165201187</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.004364242777228355</v>
+        <v>0.1336777061223984</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.02325324155390263</v>
+        <v>0.07899647951126099</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.02377570420503616</v>
+        <v>0.07059276849031448</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.007351052481681108</v>
+        <v>0.3559327721595764</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.02669362165033817</v>
+        <v>0.05755996704101562</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0004260012065060437</v>
+        <v>0.2221548706293106</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.002674797782674432</v>
+        <v>0.04500455781817436</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.003739714156836271</v>
+        <v>0.08001212775707245</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.004892659373581409</v>
+        <v>0.008892375975847244</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.00749110896140337</v>
+        <v>0.05715600028634071</v>
       </c>
       <c r="BR7" t="n">
-        <v>2.556946128606796e-05</v>
+        <v>0.07685220241546631</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.003369607497006655</v>
+        <v>0.04345510900020599</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.008363114669919014</v>
+        <v>0.08747869729995728</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.008615745231509209</v>
+        <v>0.129120871424675</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05087438225746155</v>
+        <v>0.7995388507843018</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.007723744492977858</v>
+        <v>0.01168723031878471</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.007409235462546349</v>
+        <v>0.5498671531677246</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.006632164120674133</v>
+        <v>0.1420229077339172</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.006779537536203861</v>
+        <v>0.277757316827774</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0007860658224672079</v>
+        <v>0.1078708842396736</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.004016224760562181</v>
+        <v>0.005250297486782074</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.007715796120464802</v>
+        <v>0.1162681728601456</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.001401909627020359</v>
+        <v>0.02914600446820259</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01885522529482841</v>
+        <v>0.403990626335144</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.004045740235596895</v>
+        <v>0.03647739440202713</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01365259289741516</v>
+        <v>0.3681822419166565</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002622315194457769</v>
+        <v>0.01060344465076923</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001854787580668926</v>
+        <v>0.02207243256270885</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.004166629165410995</v>
+        <v>0.00975402258336544</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0001175494398921728</v>
+        <v>0.1049440279603004</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.003675164887681603</v>
+        <v>0.09250716865062714</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.02041272632777691</v>
+        <v>0.05515016242861748</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.006123355124145746</v>
+        <v>0.560968279838562</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.002015384146943688</v>
+        <v>0.09913302212953568</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.02354446612298489</v>
+        <v>0.4244083762168884</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.02597791142761707</v>
+        <v>0.1145429462194443</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.02634956128895283</v>
+        <v>0.1017597988247871</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.007462409324944019</v>
+        <v>0.1033895313739777</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.02791601605713367</v>
+        <v>0.09306462109088898</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.003521081525832415</v>
+        <v>0.1114830896258354</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0004538390785455704</v>
+        <v>0.08139613270759583</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.02042356878519058</v>
+        <v>0.4339675903320312</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.006613502278923988</v>
+        <v>0.03200794011354446</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.01861724629998207</v>
+        <v>0.3879020810127258</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.002446854021400213</v>
+        <v>0.04538113623857498</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.005644726566970348</v>
+        <v>0.01741007342934608</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.004721352364867926</v>
+        <v>0.04284543916583061</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0008759326301515102</v>
+        <v>0.08125969022512436</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0007258056430146098</v>
+        <v>0.08892898261547089</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.002414104295894504</v>
+        <v>0.2781694829463959</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.02265916205942631</v>
+        <v>0.5460586547851562</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.01056359987705946</v>
+        <v>0.1763265430927277</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.02179607748985291</v>
+        <v>0.5139427185058594</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03007182106375694</v>
+        <v>0.1297587454319</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.002758627291768789</v>
+        <v>0.3729324340820312</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.000325747299939394</v>
+        <v>0.09448087960481644</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.00675140880048275</v>
+        <v>0.5557218790054321</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.009384775534272194</v>
+        <v>0.06862284988164902</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.002477800706401467</v>
+        <v>0.1462470144033432</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01533113140612841</v>
+        <v>0.1846567988395691</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0113766435533762</v>
+        <v>0.03689087554812431</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.001312506617978215</v>
+        <v>0.261527419090271</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01370842009782791</v>
+        <v>0.185329258441925</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0008843936957418919</v>
+        <v>0.1215451657772064</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.001316860667429864</v>
+        <v>0.08681505173444748</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0008894475176930428</v>
+        <v>0.09498446434736252</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.005514946300536394</v>
+        <v>0.4742013216018677</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.007105171214789152</v>
+        <v>0.02176482602953911</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.003857778618112206</v>
+        <v>0.2148171663284302</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.01871313899755478</v>
+        <v>0.04883289337158203</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.008444300852715969</v>
+        <v>0.2752862870693207</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0108821764588356</v>
+        <v>0.03432603180408478</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.00912904366850853</v>
+        <v>0.3025164008140564</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.007030786015093327</v>
+        <v>0.04311372712254524</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.005794440861791372</v>
+        <v>0.5054640173912048</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.00164194474928081</v>
+        <v>0.3924092054367065</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.002503537107259035</v>
+        <v>0.1954749822616577</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.01845244877040386</v>
+        <v>0.3285412788391113</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.00211468618363142</v>
+        <v>0.07608257234096527</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01432785950601101</v>
+        <v>0.2603470981121063</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02593562379479408</v>
+        <v>0.1034353822469711</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0002562390873208642</v>
+        <v>0.06071889400482178</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.006813428830355406</v>
+        <v>0.004990000277757645</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001014614477753639</v>
+        <v>0.09190929681062698</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.003753830678761005</v>
+        <v>0.01076596602797508</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001684568705968559</v>
+        <v>0.1268212348222733</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.010080860927701</v>
+        <v>0.3625103831291199</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.01515545044094324</v>
+        <v>0.1291240751743317</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.01941647939383984</v>
+        <v>0.2980452477931976</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.02029433660209179</v>
+        <v>0.09384813904762268</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01759510487318039</v>
+        <v>0.330680638551712</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.008882801979780197</v>
+        <v>0.1575774848461151</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.001935104955919087</v>
+        <v>0.07672479003667831</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.002310182666406035</v>
+        <v>0.1774569600820541</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.002173455664888024</v>
+        <v>0.03865718096494675</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.02128825150430202</v>
+        <v>0.4835171401500702</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.003615269903093576</v>
+        <v>0.005714604631066322</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.01646502688527107</v>
+        <v>0.4288104772567749</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.003379503265023232</v>
+        <v>0.0371590182185173</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.005070854444056749</v>
+        <v>0.01780925132334232</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.00696913106366992</v>
+        <v>0.03933452069759369</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.001132537377998233</v>
+        <v>0.1312752515077591</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.003346953075379133</v>
+        <v>0.08001299202442169</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.004034816287457943</v>
+        <v>0.04853738844394684</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.006349759176373482</v>
+        <v>0.1402903497219086</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.004267073236405849</v>
+        <v>0.23599673807621</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.001187484594993293</v>
+        <v>0.05723531544208527</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0005125908646732569</v>
+        <v>0.008121781051158905</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.006452021189033985</v>
+        <v>0.01473224349319935</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.008128251880407333</v>
+        <v>0.003935720771551132</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.005148555152118206</v>
+        <v>0.0918804407119751</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.009216699749231339</v>
+        <v>0.3222676515579224</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.00142525602132082</v>
+        <v>0.1329111903905869</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.004335277713835239</v>
+        <v>0.5363577604293823</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.002725188154727221</v>
+        <v>0.2919130325317383</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01187607925385237</v>
+        <v>0.6316781044006348</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0185178816318512</v>
+        <v>0.2172439247369766</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.000311987241730094</v>
+        <v>0.088414266705513</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.009579116478562355</v>
+        <v>0.0003722496330738068</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.004622163251042366</v>
+        <v>0.03403481096029282</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.008055771701037884</v>
+        <v>0.3424621522426605</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0133537407964468</v>
+        <v>0.08603706955909729</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.005112184677273035</v>
+        <v>0.3187088668346405</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.006193093024194241</v>
+        <v>0.2024055570363998</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.005944674834609032</v>
+        <v>0.2068788558244705</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.01252804044634104</v>
+        <v>0.4690952897071838</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.008236964233219624</v>
+        <v>0.002392161637544632</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.02808329276740551</v>
+        <v>0.3201932013034821</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.009560244157910347</v>
+        <v>0.1070915013551712</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.005417875945568085</v>
+        <v>0.1136437654495239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.003512197639793158</v>
+        <v>0.09089333564043045</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04965308681130409</v>
+        <v>0.7906311750411987</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004162178840488195</v>
+        <v>0.01678361743688583</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0232908483594656</v>
+        <v>0.1462884843349457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004132565576583147</v>
+        <v>0.0289517417550087</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02951814606785774</v>
+        <v>0.9992201924324036</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001139232655987144</v>
+        <v>0.1838658303022385</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01600266993045807</v>
+        <v>0.3809411823749542</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002874935511499643</v>
+        <v>0.01638936996459961</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009729352779686451</v>
+        <v>0.01123360171914101</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03939186781644821</v>
+        <v>0.9537010192871094</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002190262079238892</v>
+        <v>0.05369503796100616</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02203446626663208</v>
+        <v>0.1254529356956482</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003398691304028034</v>
+        <v>0.3967592418193817</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03240690752863884</v>
+        <v>0.8457346558570862</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002604924840852618</v>
+        <v>0.00490539101883769</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001460517756640911</v>
+        <v>0.1682697236537933</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003196564735844731</v>
+        <v>0.07720822840929031</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003234401112422347</v>
+        <v>0.1443658173084259</v>
       </c>
       <c r="T8" t="n">
-        <v>0.006976380944252014</v>
+        <v>0.1230746582150459</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003037272952497005</v>
+        <v>0.3259046673774719</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000505543895997107</v>
+        <v>0.07483085244894028</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002404768718406558</v>
+        <v>0.1373900324106216</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001718649407848716</v>
+        <v>0.2064281404018402</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005300344433635473</v>
+        <v>0.2302809655666351</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004331956617534161</v>
+        <v>0.2448125183582306</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002508145291358232</v>
+        <v>0.02280981093645096</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003176970407366753</v>
+        <v>0.1095683425664902</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.007089105900377035</v>
+        <v>0.2495952546596527</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0004186122096143663</v>
+        <v>0.1372453570365906</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0002867941511794925</v>
+        <v>0.3004775941371918</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002836438361555338</v>
+        <v>0.1365968436002731</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005405839998275042</v>
+        <v>0.1037032231688499</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002237661043182015</v>
+        <v>0.09654424339532852</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001827336382120848</v>
+        <v>0.3813329339027405</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002197699155658484</v>
+        <v>0.1864399909973145</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.003432400058954954</v>
+        <v>0.03091301210224628</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.007786390837281942</v>
+        <v>0.1095038503408432</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0005065618315711617</v>
+        <v>0.01159545034170151</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002982999663800001</v>
+        <v>0.06299492716789246</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006023097317665815</v>
+        <v>0.07865195721387863</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.00720652611926198</v>
+        <v>0.1773909628391266</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002800175920128822</v>
+        <v>0.2331241965293884</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.003280185163021088</v>
+        <v>0.2756932973861694</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.006027922034263611</v>
+        <v>0.1464752852916718</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002353018149733543</v>
+        <v>0.1429148614406586</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.03060699254274368</v>
+        <v>0.8875323534011841</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0005419355584308505</v>
+        <v>0.1537000834941864</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0007303999736905098</v>
+        <v>0.08321464061737061</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001920145936310291</v>
+        <v>0.3053872883319855</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0224493183195591</v>
+        <v>0.4945474565029144</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.006302836816757917</v>
+        <v>0.1685324460268021</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.008844070136547089</v>
+        <v>0.02506915479898453</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.008187205530703068</v>
+        <v>0.0115515012294054</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0006415368989109993</v>
+        <v>0.1174400821328163</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01022294629365206</v>
+        <v>0.08710170537233353</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.01228417921811342</v>
+        <v>0.1331843435764313</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.005574371665716171</v>
+        <v>0.3183622658252716</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01141472160816193</v>
+        <v>0.0390942208468914</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.008256289176642895</v>
+        <v>0.2403199523687363</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.003513009054586291</v>
+        <v>0.2242687940597534</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.009926952421665192</v>
+        <v>0.2761432230472565</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.004346093628555536</v>
+        <v>0.2152839303016663</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0007204801077023149</v>
+        <v>0.128083199262619</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.002514813095331192</v>
+        <v>0.1858371645212173</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.005432019010186195</v>
+        <v>0.05161565169692039</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.005000507924705744</v>
+        <v>0.1211421936750412</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002017939696088433</v>
+        <v>0.07736454904079437</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.001343496842309833</v>
+        <v>0.151495561003685</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.00377226946875453</v>
+        <v>0.3389309644699097</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002729086671024561</v>
+        <v>0.07976020872592926</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0001411887351423502</v>
+        <v>0.09976179152727127</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002319547813385725</v>
+        <v>0.05586656183004379</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.01573745161294937</v>
+        <v>0.3403184115886688</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.006359185092151165</v>
+        <v>0.251928985118866</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0001967842690646648</v>
+        <v>0.1372629851102829</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.00358250318095088</v>
+        <v>0.1863613575696945</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01062723156064749</v>
+        <v>0.476126104593277</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.001854392467066646</v>
+        <v>0.3450724482536316</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.005227946676313877</v>
+        <v>0.1562552154064178</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.005399383138865232</v>
+        <v>0.09747809171676636</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0007050513522699475</v>
+        <v>0.04587278887629509</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.008622483350336552</v>
+        <v>0.2682859599590302</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.005067063961178064</v>
+        <v>0.03342551365494728</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003927614074200392</v>
+        <v>0.003162292763590813</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002754593268036842</v>
+        <v>0.05297998711466789</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.003830899950116873</v>
+        <v>0.2488252222537994</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.003446733113378286</v>
+        <v>0.1113349124789238</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.002453085733577609</v>
+        <v>0.06220110505819321</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.002535204868763685</v>
+        <v>0.007935940288007259</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.006633197423070669</v>
+        <v>0.1465962380170822</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001094743027351797</v>
+        <v>0.5575641393661499</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001073629362508655</v>
+        <v>0.3360113799571991</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.01305686496198177</v>
+        <v>0.3422193825244904</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.002243979601189494</v>
+        <v>0.05674942582845688</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0009041158482432365</v>
+        <v>0.2515778839588165</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.00716444430872798</v>
+        <v>0.003744714893400669</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.008488862775266171</v>
+        <v>0.1776461154222488</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0008753354195505381</v>
+        <v>0.09919966757297516</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0001351304235868156</v>
+        <v>0.003284666687250137</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.007696337066590786</v>
+        <v>0.2431083917617798</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.005265028215944767</v>
+        <v>0.009546352550387383</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.006221562623977661</v>
+        <v>0.01057434733957052</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002845772542059422</v>
+        <v>0.02578371949493885</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.00418802397325635</v>
+        <v>0.225998729467392</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.002628704067319632</v>
+        <v>0.1067629233002663</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.004559400025755167</v>
+        <v>0.006244970485568047</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.002206894569098949</v>
+        <v>0.02079842239618301</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.004529483150690794</v>
+        <v>0.2908114194869995</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.002735029207542539</v>
+        <v>0.1544801443815231</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.001295929425396025</v>
+        <v>0.2273190319538116</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.009552821516990662</v>
+        <v>0.1086676493287086</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0002755540190264583</v>
+        <v>0.1484060734510422</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.005729075521230698</v>
+        <v>0.3230577111244202</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.005343955475836992</v>
+        <v>0.1720395535230637</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.01272944733500481</v>
+        <v>0.2203082144260406</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.005694078747183084</v>
+        <v>0.2623479962348938</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.002130706328898668</v>
+        <v>0.003577969968318939</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.00152019108645618</v>
+        <v>0.09383063018321991</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.004514421802014112</v>
+        <v>0.06895631551742554</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.00377805158495903</v>
+        <v>0.06925117969512939</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0009155198931694031</v>
+        <v>0.01938730105757713</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0008422661339864135</v>
+        <v>0.1055926606059074</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.00272598466835916</v>
+        <v>0.09852567315101624</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.00137384282425046</v>
+        <v>0.1182103306055069</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.003964743111282587</v>
+        <v>0.02526569738984108</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.001576518174260855</v>
+        <v>0.05696872621774673</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.003333268454298377</v>
+        <v>0.1438978761434555</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.005734026897698641</v>
+        <v>0.009079735726118088</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.005274595692753792</v>
+        <v>0.02806754782795906</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.001053423620760441</v>
+        <v>0.08235841244459152</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.000365370768122375</v>
+        <v>0.1421741992235184</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.001452256110496819</v>
+        <v>0.03824709355831146</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0001253667287528515</v>
+        <v>0.06684692949056625</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.003134205937385559</v>
+        <v>0.2038138508796692</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.002097653457894921</v>
+        <v>0.08882711827754974</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.006800755392760038</v>
+        <v>0.09435852617025375</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.002749884501099586</v>
+        <v>0.1402894258499146</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.002000232227146626</v>
+        <v>0.05065517872571945</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0002821161178871989</v>
+        <v>0.02495148777961731</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0004865840310230851</v>
+        <v>0.2827407717704773</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.006086350418627262</v>
+        <v>0.02894696779549122</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.001663652947172523</v>
+        <v>0.02489536255598068</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0003131671110168099</v>
+        <v>0.006205432116985321</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0001668009208515286</v>
+        <v>0.04676688089966774</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.003161245957016945</v>
+        <v>0.147152304649353</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.006606607232242823</v>
+        <v>0.1752060949802399</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.003894904162734747</v>
+        <v>0.05647335946559906</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.002789948601275682</v>
+        <v>0.2031854540109634</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.004368346184492111</v>
+        <v>0.1965561211109161</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.005210600793361664</v>
+        <v>0.03694942593574524</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.008872157894074917</v>
+        <v>0.03363735228776932</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.002159454161301255</v>
+        <v>0.01851557940244675</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.000367277127224952</v>
+        <v>0.0208554845303297</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.007099197246134281</v>
+        <v>0.2639263570308685</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.003744320478290319</v>
+        <v>0.01551460474729538</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.003337871981784701</v>
+        <v>0.01504383329302073</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.002980305813252926</v>
+        <v>0.1068817153573036</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.003496774006634951</v>
+        <v>0.2402283400297165</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.004569444339722395</v>
+        <v>0.1131780371069908</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.00304682832211256</v>
+        <v>0.07122735679149628</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.003890070132911205</v>
+        <v>0.02502137050032616</v>
       </c>
       <c r="FG8" t="n">
-        <v>2.05611577257514e-05</v>
+        <v>0.1406025886535645</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.003087940625846386</v>
+        <v>0.1578286439180374</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.005596472881734371</v>
+        <v>0.09976789355278015</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.01099685300141573</v>
+        <v>0.09615865349769592</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.002634731354191899</v>
+        <v>0.04941968619823456</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.005655082874000072</v>
+        <v>0.2752770483493805</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0008391074370592833</v>
+        <v>0.2196215242147446</v>
       </c>
       <c r="FN8" t="n">
-        <v>1.223653089255095e-05</v>
+        <v>0.2450160682201385</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.005003792233765125</v>
+        <v>0.137957364320755</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.004044340923428535</v>
+        <v>0.2753978371620178</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01320018619298935</v>
+        <v>0.07856603711843491</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.002650436712428927</v>
+        <v>0.03630119562149048</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.003712617792189121</v>
+        <v>0.3526402115821838</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001266781939193606</v>
+        <v>0.1880493313074112</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.008347026072442532</v>
+        <v>0.1718409955501556</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.005647813901305199</v>
+        <v>0.01039068400859833</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.005807060748338699</v>
+        <v>0.1441260129213333</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.001722847693599761</v>
+        <v>0.03425560146570206</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.007972326129674911</v>
+        <v>0.2565025091171265</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.002103631617501378</v>
+        <v>0.02851307205855846</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.001851240289397538</v>
+        <v>0.04189125448465347</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.000585062662139535</v>
+        <v>0.04376431554555893</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.004869410302489996</v>
+        <v>0.3430101573467255</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.007147409953176975</v>
+        <v>0.2534734904766083</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01750560477375984</v>
+        <v>0.0387580506503582</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.002069782000035048</v>
+        <v>0.04908395186066628</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.00235792575404048</v>
+        <v>0.2577957808971405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.031930464203469e-05</v>
+        <v>0.008211778476834297</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002162385964766145</v>
+        <v>0.3017407357692719</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0003028797509614378</v>
+        <v>0.03772718831896782</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001377225504256785</v>
+        <v>0.3279918432235718</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005087286699563265</v>
+        <v>0.1642516702413559</v>
       </c>
       <c r="F9" t="n">
-        <v>4.94987798447255e-05</v>
+        <v>0.2062667012214661</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000233968865359202</v>
+        <v>0.08139344304800034</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002865191781893373</v>
+        <v>0.1245259419083595</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001104589973692782</v>
+        <v>0.01845983043313026</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001668596814852208</v>
+        <v>0.07434909045696259</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001740228733979166</v>
+        <v>0.2623699307441711</v>
       </c>
       <c r="L9" t="n">
-        <v>8.67776179802604e-05</v>
+        <v>0.107315219938755</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001333825523033738</v>
+        <v>0.4524701237678528</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0006604306399822235</v>
+        <v>0.2467921376228333</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002002090332098305</v>
+        <v>0.1757979094982147</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001403972710249946</v>
+        <v>0.08257171511650085</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001957908243639395</v>
+        <v>0.006109651178121567</v>
       </c>
       <c r="R9" t="n">
-        <v>5.555322059080936e-05</v>
+        <v>0.02277230285108089</v>
       </c>
       <c r="S9" t="n">
-        <v>5.926769154029898e-05</v>
+        <v>0.02564992010593414</v>
       </c>
       <c r="T9" t="n">
-        <v>0.000401182594941929</v>
+        <v>0.01707456633448601</v>
       </c>
       <c r="U9" t="n">
-        <v>1.577601506141946e-05</v>
+        <v>0.02237090282142162</v>
       </c>
       <c r="V9" t="n">
-        <v>6.422619480872527e-05</v>
+        <v>0.0003844099119305611</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002304534282302484</v>
+        <v>0.07133142650127411</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001977950596483424</v>
+        <v>0.07067151367664337</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002394798066234216</v>
+        <v>0.002893813885748386</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.434938844293356e-05</v>
+        <v>0.005068821832537651</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0001238020340679213</v>
+        <v>0.0472971573472023</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0003290779422968626</v>
+        <v>0.02240594662725925</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0004154573834966868</v>
+        <v>0.1248276680707932</v>
       </c>
       <c r="AD9" t="n">
-        <v>8.762982906773686e-05</v>
+        <v>0.05002541840076447</v>
       </c>
       <c r="AE9" t="n">
-        <v>7.16406138963066e-05</v>
+        <v>0.01996209472417831</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.526302316458896e-05</v>
+        <v>0.02043872326612473</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001204325817525387</v>
+        <v>0.06165633350610733</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.00010393449338153</v>
+        <v>0.009581230580806732</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.725216371705756e-05</v>
+        <v>0.05878244712948799</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9.527519068797119e-06</v>
+        <v>0.0651245042681694</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0001129015581682324</v>
+        <v>0.02471039816737175</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0002561474393587559</v>
+        <v>0.09127315133810043</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.916389373946004e-05</v>
+        <v>0.06298817694187164</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.924795964849181e-05</v>
+        <v>0.03300752863287926</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0001128016083384864</v>
+        <v>0.00840274803340435</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0002037761296378449</v>
+        <v>0.08468493074178696</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001255855750059709</v>
+        <v>0.05652900412678719</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0002039549581240863</v>
+        <v>0.03018211200833321</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.81114979670383e-05</v>
+        <v>0.0221197996288538</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0001823999627958983</v>
+        <v>0.04916148260235786</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.001574264839291573</v>
+        <v>0.2213937044143677</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.766154597746208e-05</v>
+        <v>0.01506621949374676</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0003766166628338397</v>
+        <v>0.1865178644657135</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.902659227605909e-05</v>
+        <v>0.2484022974967957</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0001552109024487436</v>
+        <v>0.06590911000967026</v>
       </c>
       <c r="AZ9" t="n">
-        <v>8.883430564310402e-05</v>
+        <v>0.01571238599717617</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.07600881671533e-05</v>
+        <v>0.08889562636613846</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.54354345088359e-05</v>
+        <v>0.03178052976727486</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0001456690515624359</v>
+        <v>0.006851056590676308</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0003903830656781793</v>
+        <v>0.07004334032535553</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0003805839514825493</v>
+        <v>0.0657341331243515</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0002526273019611835</v>
+        <v>0.06378278136253357</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0006408639601431787</v>
+        <v>0.1230766624212265</v>
       </c>
       <c r="BH9" t="n">
-        <v>1.642053393879905e-05</v>
+        <v>0.07224024087190628</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0002975481329485774</v>
+        <v>0.0301922895014286</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0001940592919709161</v>
+        <v>0.1461681127548218</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.920540595776401e-05</v>
+        <v>0.05306223034858704</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0003370370541233569</v>
+        <v>0.004402792081236839</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0002701394259929657</v>
+        <v>0.06607281416654587</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0001956179039552808</v>
+        <v>0.0359855443239212</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.990187178715132e-05</v>
+        <v>0.01611297391355038</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0002570226206444204</v>
+        <v>0.1220964267849922</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0001727686903905123</v>
+        <v>0.009231504052877426</v>
       </c>
       <c r="BR9" t="n">
-        <v>1.112441896111704e-05</v>
+        <v>0.007246926426887512</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.0779377236031e-05</v>
+        <v>0.0008552772924304008</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0001162454718723893</v>
+        <v>0.0008279494941234589</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0001035733730532229</v>
+        <v>0.02694013714790344</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0007929964922368526</v>
+        <v>0.09889282286167145</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0003593620203901082</v>
+        <v>0.01548194233328104</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001427660754416138</v>
+        <v>0.1250917911529541</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0002087409666273743</v>
+        <v>0.124738834798336</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0001103158574551344</v>
+        <v>0.08906801044940948</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001037959227687679</v>
+        <v>0.04777219146490097</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.671615872415714e-05</v>
+        <v>0.01136324927210808</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.140420737210661e-05</v>
+        <v>0.02636838145554066</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.28438111662399e-05</v>
+        <v>0.008600545115768909</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0003806773747783154</v>
+        <v>0.08118421584367752</v>
       </c>
       <c r="CF9" t="n">
-        <v>9.106069046538323e-05</v>
+        <v>0.006978834979236126</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0001270853390451521</v>
+        <v>0.1052640825510025</v>
       </c>
       <c r="CH9" t="n">
-        <v>9.798636165214702e-05</v>
+        <v>0.0265534408390522</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.219326597696636e-05</v>
+        <v>0.02765148505568504</v>
       </c>
       <c r="CJ9" t="n">
-        <v>7.466358511010185e-05</v>
+        <v>0.005589390639215708</v>
       </c>
       <c r="CK9" t="n">
-        <v>2.4101300368784e-05</v>
+        <v>0.04532603174448013</v>
       </c>
       <c r="CL9" t="n">
-        <v>3.866045881295577e-05</v>
+        <v>0.01335810497403145</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0005100908456370234</v>
+        <v>0.01509435940533876</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0003336657537147403</v>
+        <v>0.1951974630355835</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.972131576621905e-05</v>
+        <v>0.06624297797679901</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0004825488722417504</v>
+        <v>0.08389383554458618</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0004234371590428054</v>
+        <v>0.04857484623789787</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0003351770283188671</v>
+        <v>0.01198837254196405</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0002063315187115222</v>
+        <v>0.03974917158484459</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0005033588968217373</v>
+        <v>0.1087536364793777</v>
       </c>
       <c r="CU9" t="n">
-        <v>5.353215965442359e-05</v>
+        <v>0.0467340499162674</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.655000207596458e-05</v>
+        <v>0.00375168863683939</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0003374374937266111</v>
+        <v>0.07861329615116119</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0001378128072246909</v>
+        <v>0.01305744983255863</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0002151064982172102</v>
+        <v>0.1174108311533928</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001127371288021095</v>
+        <v>0.02250402234494686</v>
       </c>
       <c r="DA9" t="n">
-        <v>3.564425787772052e-05</v>
+        <v>0.026305191218853</v>
       </c>
       <c r="DB9" t="n">
-        <v>5.382363087846898e-05</v>
+        <v>0.01372566539794207</v>
       </c>
       <c r="DC9" t="n">
-        <v>3.157735773129389e-05</v>
+        <v>0.04161825403571129</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.187599188298918e-06</v>
+        <v>0.01330072153359652</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0001215209777001292</v>
+        <v>0.07596343010663986</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0002728051040321589</v>
+        <v>0.09470211714506149</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0001631862105568871</v>
+        <v>0.04079626500606537</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0005344727542251348</v>
+        <v>0.106122612953186</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0001134058475145139</v>
+        <v>0.002740031108260155</v>
       </c>
       <c r="DJ9" t="n">
-        <v>5.849653098266572e-05</v>
+        <v>0.04885281249880791</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0002008561423281208</v>
+        <v>0.04802413284778595</v>
       </c>
       <c r="DL9" t="n">
-        <v>8.191350207198411e-05</v>
+        <v>0.2058427035808563</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0001885909005068243</v>
+        <v>0.03908525034785271</v>
       </c>
       <c r="DN9" t="n">
-        <v>8.119010453810915e-05</v>
+        <v>0.06055648252367973</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001959604996955022</v>
+        <v>0.03961313143372536</v>
       </c>
       <c r="DP9" t="n">
-        <v>5.915107612963766e-05</v>
+        <v>0.01662091352045536</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0001601869444129989</v>
+        <v>0.0760050043463707</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0002706059603951871</v>
+        <v>0.07892388105392456</v>
       </c>
       <c r="DS9" t="n">
-        <v>6.900829612277448e-05</v>
+        <v>0.100194051861763</v>
       </c>
       <c r="DT9" t="n">
-        <v>6.929966912139207e-05</v>
+        <v>0.03247357904911041</v>
       </c>
       <c r="DU9" t="n">
-        <v>5.750738637289032e-05</v>
+        <v>0.005404994823038578</v>
       </c>
       <c r="DV9" t="n">
-        <v>4.763456672662869e-06</v>
+        <v>0.1077318266034126</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.081712071027141e-05</v>
+        <v>0.0199388787150383</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0001523045793874189</v>
+        <v>0.04792038723826408</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0001365732314297929</v>
+        <v>0.01032690703868866</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.080520087270997e-05</v>
+        <v>0.03307934105396271</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0003503223997540772</v>
+        <v>0.02550156228244305</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0001279775897273794</v>
+        <v>0.003777401521801949</v>
       </c>
       <c r="EC9" t="n">
-        <v>5.57734165340662e-05</v>
+        <v>0.02756194025278091</v>
       </c>
       <c r="ED9" t="n">
-        <v>3.537025622790679e-05</v>
+        <v>0.1794918477535248</v>
       </c>
       <c r="EE9" t="n">
-        <v>9.781360859051347e-07</v>
+        <v>0.08102996647357941</v>
       </c>
       <c r="EF9" t="n">
-        <v>4.722765879705548e-06</v>
+        <v>0.04395791888237</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0003097568114753813</v>
+        <v>0.06021837890148163</v>
       </c>
       <c r="EH9" t="n">
-        <v>6.96190181770362e-05</v>
+        <v>0.006007520481944084</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0002836289640981704</v>
+        <v>0.07353468239307404</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.000192995517863892</v>
+        <v>0.03812975436449051</v>
       </c>
       <c r="EK9" t="n">
-        <v>1.011966560326982e-05</v>
+        <v>0.06620264053344727</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001094469116651453</v>
+        <v>0.01308912970125675</v>
       </c>
       <c r="EM9" t="n">
-        <v>3.186847607139498e-05</v>
+        <v>0.06145158782601357</v>
       </c>
       <c r="EN9" t="n">
-        <v>2.086668246192858e-05</v>
+        <v>0.00540635734796524</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0001095698098652065</v>
+        <v>0.006029029842466116</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0002914402284659445</v>
+        <v>0.06559854745864868</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0002728443942032754</v>
+        <v>0.003840158693492413</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0002167810889659449</v>
+        <v>0.0807778462767601</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.000154373628902249</v>
+        <v>0.03338279947638512</v>
       </c>
       <c r="ET9" t="n">
-        <v>1.061833427229431e-05</v>
+        <v>0.135784924030304</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.000146948077599518</v>
+        <v>0.05087060481309891</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0001060341310221702</v>
+        <v>0.0224332008510828</v>
       </c>
       <c r="EW9" t="n">
-        <v>2.384248182352167e-05</v>
+        <v>0.08346351236104965</v>
       </c>
       <c r="EX9" t="n">
-        <v>5.094152948004194e-05</v>
+        <v>0.01291730254888535</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0003701082605402917</v>
+        <v>0.09559708833694458</v>
       </c>
       <c r="EZ9" t="n">
-        <v>8.096054079942405e-05</v>
+        <v>0.002553662750869989</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001696401595836505</v>
+        <v>0.1188610792160034</v>
       </c>
       <c r="FB9" t="n">
-        <v>8.182282908819616e-05</v>
+        <v>0.01999500207602978</v>
       </c>
       <c r="FC9" t="n">
-        <v>7.752590317977592e-05</v>
+        <v>0.02121647074818611</v>
       </c>
       <c r="FD9" t="n">
-        <v>8.569662168156356e-05</v>
+        <v>0.004409210756421089</v>
       </c>
       <c r="FE9" t="n">
-        <v>3.693765756906942e-05</v>
+        <v>0.06153672561049461</v>
       </c>
       <c r="FF9" t="n">
-        <v>4.223584619467147e-05</v>
+        <v>0.02202748507261276</v>
       </c>
       <c r="FG9" t="n">
-        <v>6.737804505974054e-05</v>
+        <v>0.01600748114287853</v>
       </c>
       <c r="FH9" t="n">
-        <v>6.449638021877035e-05</v>
+        <v>0.0005996818654239178</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0001231427304446697</v>
+        <v>0.02188265137374401</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0001899281778605655</v>
+        <v>0.04378245770931244</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0002080197009490803</v>
+        <v>0.06619898974895477</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0002229698002338409</v>
+        <v>0.0005168539937585592</v>
       </c>
       <c r="FM9" t="n">
-        <v>6.099063830333762e-05</v>
+        <v>0.01845451258122921</v>
       </c>
       <c r="FN9" t="n">
-        <v>6.121023034211248e-06</v>
+        <v>0.03755833581089973</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001344389893347397</v>
+        <v>0.04668367281556129</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0001581732067279518</v>
+        <v>0.02443999610841274</v>
       </c>
       <c r="FQ9" t="n">
-        <v>9.571531700203195e-05</v>
+        <v>0.1815247982740402</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0001629602920729667</v>
+        <v>0.07544195652008057</v>
       </c>
       <c r="FS9" t="n">
-        <v>1.91412509593647e-05</v>
+        <v>0.1107278019189835</v>
       </c>
       <c r="FT9" t="n">
-        <v>4.490357241593301e-05</v>
+        <v>0.1459039300680161</v>
       </c>
       <c r="FU9" t="n">
-        <v>3.313143315608613e-05</v>
+        <v>0.03974951058626175</v>
       </c>
       <c r="FV9" t="n">
-        <v>9.340090036857873e-05</v>
+        <v>0.05099546909332275</v>
       </c>
       <c r="FW9" t="n">
-        <v>2.526598109398037e-06</v>
+        <v>0.1140016689896584</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001424658257747069</v>
+        <v>0.04956349730491638</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0003174418234266341</v>
+        <v>0.02449237555265427</v>
       </c>
       <c r="FZ9" t="n">
-        <v>8.979453559732065e-05</v>
+        <v>0.07692156732082367</v>
       </c>
       <c r="GA9" t="n">
-        <v>3.375867527211085e-05</v>
+        <v>0.03299371898174286</v>
       </c>
       <c r="GB9" t="n">
-        <v>2.003009285544977e-05</v>
+        <v>0.05099561810493469</v>
       </c>
       <c r="GC9" t="n">
-        <v>6.85951454215683e-05</v>
+        <v>0.1497504264116287</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0001259811979252845</v>
+        <v>0.03881346806883812</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0003437410341575742</v>
+        <v>0.09370036423206329</v>
       </c>
       <c r="GF9" t="n">
-        <v>7.896800525486469e-05</v>
+        <v>0.01122480072081089</v>
       </c>
       <c r="GG9" t="n">
-        <v>3.530871617840603e-05</v>
+        <v>0.03693072125315666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.008499178104102612</v>
+        <v>1.022961020469666</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00970682967454195</v>
+        <v>0.4954018592834473</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01356310769915581</v>
+        <v>0.5448582172393799</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001163738546893001</v>
+        <v>0.345360666513443</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006787130143493414</v>
+        <v>0.4797086417675018</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00661865621805191</v>
+        <v>0.4602422118186951</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003393606515601277</v>
+        <v>0.517727255821228</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001055062981322408</v>
+        <v>0.06876786053180695</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001349973026663065</v>
+        <v>0.05594571679830551</v>
       </c>
       <c r="J10" t="n">
-        <v>0.003365600947290659</v>
+        <v>1.08656919002533</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004121009260416031</v>
+        <v>0.2900676727294922</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009573264047503471</v>
+        <v>0.498248815536499</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00763384997844696</v>
+        <v>0.2228914201259613</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01075427792966366</v>
+        <v>0.3190310299396515</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002164536854252219</v>
+        <v>0.1675224304199219</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0002983426675200462</v>
+        <v>0.7128424048423767</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001637077075429261</v>
+        <v>0.06455116719007492</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005735991522669792</v>
+        <v>0.1138431802392006</v>
       </c>
       <c r="S10" t="n">
-        <v>0.003542885184288025</v>
+        <v>0.103457547724247</v>
       </c>
       <c r="T10" t="n">
-        <v>0.005772395059466362</v>
+        <v>0.5816621780395508</v>
       </c>
       <c r="U10" t="n">
-        <v>0.007232104428112507</v>
+        <v>0.190704733133316</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002401644829660654</v>
+        <v>0.2350351065397263</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001424751128070056</v>
+        <v>0.2102668434381485</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0006688187713734806</v>
+        <v>0.2626627087593079</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0001960722438525409</v>
+        <v>0.05709125846624374</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0006691477028653026</v>
+        <v>0.03521744161844254</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0003031452943105251</v>
+        <v>0.1133489459753036</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0002933915238827467</v>
+        <v>0.4486070871353149</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002229778794571757</v>
+        <v>0.1554162502288818</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.002807889599353075</v>
+        <v>0.06401386111974716</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.002085701795294881</v>
+        <v>0.05375638231635094</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001413042424246669</v>
+        <v>0.3482930064201355</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003510283771902323</v>
+        <v>0.3394482731819153</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.001177860191091895</v>
+        <v>0.1597399562597275</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.001841070014052093</v>
+        <v>0.107503741979599</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001185748027637601</v>
+        <v>0.1403318047523499</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001373986713588238</v>
+        <v>0.194031298160553</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.007238511927425861</v>
+        <v>0.6706681251525879</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.001027089543640614</v>
+        <v>0.1501419246196747</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001894080894999206</v>
+        <v>0.09828111529350281</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.004183701705187559</v>
+        <v>0.3477529883384705</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.004941381048411131</v>
+        <v>0.15899358689785</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001846927450969815</v>
+        <v>0.2028978615999222</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0006209275452420115</v>
+        <v>0.1351837515830994</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001364790252409875</v>
+        <v>0.04863773286342621</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.007095967885106802</v>
+        <v>0.7214851975440979</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0002839281223714352</v>
+        <v>0.4058475494384766</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.01119212806224823</v>
+        <v>0.2219114899635315</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.001077619846910238</v>
+        <v>0.3436828851699829</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.007444462738931179</v>
+        <v>0.4484334886074066</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.000500788853969425</v>
+        <v>0.1745071858167648</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.002965846797451377</v>
+        <v>0.1238406822085381</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0004716234398074448</v>
+        <v>0.4024614095687866</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.006677248980849981</v>
+        <v>0.2029251456260681</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.003032696899026632</v>
+        <v>0.01716797053813934</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0131157822906971</v>
+        <v>0.2377840876579285</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.00149117608089</v>
+        <v>0.010384202003479</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.005243589635938406</v>
+        <v>0.135393500328064</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0057760258205235</v>
+        <v>0.6983258724212646</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01383857149630785</v>
+        <v>0.04884380102157593</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002600011881440878</v>
+        <v>0.3387669920921326</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.007029459811747074</v>
+        <v>0.5604267120361328</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.00638252031058073</v>
+        <v>0.1066502034664154</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0002738849725574255</v>
+        <v>0.006564557552337646</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.001889570616185665</v>
+        <v>0.21170774102211</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.006030024960637093</v>
+        <v>0.01888338848948479</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.005799076519906521</v>
+        <v>0.1694908440113068</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0009437838452868164</v>
+        <v>0.06417778134346008</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.004584554117172956</v>
+        <v>0.03985283896327019</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.002769266720861197</v>
+        <v>0.18316550552845</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.002703785663470626</v>
+        <v>0.1655614376068115</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002728620311245322</v>
+        <v>0.149428978562355</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.002576492028310895</v>
+        <v>0.2975555658340454</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.002607415663078427</v>
+        <v>0.7176082134246826</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.004225813783705235</v>
+        <v>0.1000142171978951</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.001069018850103021</v>
+        <v>0.1086699441075325</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.005610744003206491</v>
+        <v>0.2858982682228088</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.003315248759463429</v>
+        <v>0.2207746505737305</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.000395581650082022</v>
+        <v>0.09390632808208466</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003788281697779894</v>
+        <v>0.07383833080530167</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.007312783040106297</v>
+        <v>0.1431966722011566</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0009783589048311114</v>
+        <v>0.1588170230388641</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0004877024912275374</v>
+        <v>0.08775512129068375</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002341635758057237</v>
+        <v>0.0574035719037056</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.001818784396164119</v>
+        <v>0.04887644201517105</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0002795422915369272</v>
+        <v>0.07793980836868286</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0002474786888342351</v>
+        <v>0.1627783626317978</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.00104774977080524</v>
+        <v>0.1253790259361267</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.001606174162589014</v>
+        <v>0.001679956912994385</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.001003040815703571</v>
+        <v>0.01283861882984638</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0004871033597737551</v>
+        <v>0.09039637446403503</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0001169894821941853</v>
+        <v>0.2204932570457458</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0001818223390728235</v>
+        <v>0.08282744884490967</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.002279856009408832</v>
+        <v>0.08835494518280029</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.005401432048529387</v>
+        <v>0.06083144992589951</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.001277240691706538</v>
+        <v>0.3257389068603516</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.004027674905955791</v>
+        <v>0.2330780476331711</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.001735615776851773</v>
+        <v>0.3289173245429993</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.002924345899373293</v>
+        <v>0.1573382318019867</v>
       </c>
       <c r="CV10" t="n">
-        <v>5.311614950187504e-05</v>
+        <v>0.2002760320901871</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.001764532295055687</v>
+        <v>0.04512797296047211</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.002247774507850409</v>
+        <v>0.09199047088623047</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.001495834323577583</v>
+        <v>0.002886159345507622</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.823727845679969e-05</v>
+        <v>0.03151688352227211</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0003334430512040854</v>
+        <v>0.2104712873697281</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0007256342796608806</v>
+        <v>0.1811559647321701</v>
       </c>
       <c r="DC10" t="n">
-        <v>3.373619983904064e-05</v>
+        <v>0.006055569276213646</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0009924424812197685</v>
+        <v>0.03790996223688126</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.003099584486335516</v>
+        <v>0.2163994610309601</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.000311938812956214</v>
+        <v>0.0547800213098526</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.01462511159479618</v>
+        <v>0.4118802845478058</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.007148363627493382</v>
+        <v>0.2042199522256851</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001865403377451003</v>
+        <v>0.4145328998565674</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0001406104565830901</v>
+        <v>1.040583610534668</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.001899868249893188</v>
+        <v>0.06853650510311127</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.00478613656014204</v>
+        <v>0.04847640544176102</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.004249499179422855</v>
+        <v>0.1464691460132599</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0008042750414460897</v>
+        <v>0.2694539427757263</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.006675765849649906</v>
+        <v>0.1860208511352539</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0007870960398577154</v>
+        <v>0.08999330550432205</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001432199031114578</v>
+        <v>0.05163686722517014</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.002408191794529557</v>
+        <v>0.4160594046115875</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.003592542605474591</v>
+        <v>0.005739827640354633</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.001188019523397088</v>
+        <v>0.01611804217100143</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.004610248375684023</v>
+        <v>0.2053930163383484</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.007035859860479832</v>
+        <v>0.269498348236084</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.000757196918129921</v>
+        <v>0.2778416275978088</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0004638272803276777</v>
+        <v>0.009779676795005798</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0009609186090528965</v>
+        <v>0.06008082628250122</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0008142655715346336</v>
+        <v>0.1392615139484406</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.004831778351217508</v>
+        <v>0.2460979968309402</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.001777645200490952</v>
+        <v>0.5373861789703369</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0003966122167184949</v>
+        <v>0.1074405759572983</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.004204933997243643</v>
+        <v>0.3089309632778168</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.004081851337105036</v>
+        <v>0.06320404261350632</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0008235644781962037</v>
+        <v>0.1344251781702042</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.008238751441240311</v>
+        <v>0.03762423992156982</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.006528296042233706</v>
+        <v>9.624287486076355e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0013767791679129</v>
+        <v>0.03956643491983414</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.002173091983422637</v>
+        <v>0.09066729247570038</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.002374784322455525</v>
+        <v>0.09221937507390976</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.001931108767166734</v>
+        <v>0.2172285914421082</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0003340702969580889</v>
+        <v>0.08044369518756866</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003608573926612735</v>
+        <v>0.1695252060890198</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.002331046853214502</v>
+        <v>0.2035912871360779</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.003230514470487833</v>
+        <v>0.09359923750162125</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.002028009155765176</v>
+        <v>0.07592236995697021</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.00061193504370749</v>
+        <v>0.04433335736393929</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.00732757430523634</v>
+        <v>0.284345805644989</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001541981124319136</v>
+        <v>0.05462050437927246</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001263867132365704</v>
+        <v>0.2915878891944885</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.002154776128008962</v>
+        <v>0.1862517148256302</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.006860783789306879</v>
+        <v>0.1510172784328461</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0006181451608426869</v>
+        <v>0.1790469288825989</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0001465511159040034</v>
+        <v>0.1083526760339737</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001961084082722664</v>
+        <v>0.08978214859962463</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001243345555849373</v>
+        <v>0.02573909610509872</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0008935814257711172</v>
+        <v>0.03868365660309792</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001818495104089379</v>
+        <v>0.1957280337810516</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0004384623316582292</v>
+        <v>0.1379060745239258</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001015926944091916</v>
+        <v>0.02006914839148521</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0003326877776999027</v>
+        <v>0.0794672891497612</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.002640750957652926</v>
+        <v>0.5616763830184937</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.004163678269833326</v>
+        <v>0.06249766051769257</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0001167619193438441</v>
+        <v>0.233306348323822</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.001390132820233703</v>
+        <v>0.1974298506975174</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.00237064273096621</v>
+        <v>0.2992074191570282</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.00259118783287704</v>
+        <v>0.06648968160152435</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0002293229481438175</v>
+        <v>0.1181251406669617</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.004033438861370087</v>
+        <v>0.1240308433771133</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0009110851678997278</v>
+        <v>0.3453816175460815</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0074030552059412</v>
+        <v>0.3072410225868225</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.001858140807598829</v>
+        <v>0.5553749203681946</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.003830063622444868</v>
+        <v>0.3301455080509186</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.004748388193547726</v>
+        <v>0.5172645449638367</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.005572934169322252</v>
+        <v>0.1073844730854034</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001298087881878018</v>
+        <v>0.2364147007465363</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.00148433493450284</v>
+        <v>0.1343147903680801</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01048062741756439</v>
+        <v>0.1707277148962021</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0002640351885929704</v>
+        <v>0.4119403064250946</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001189204631373286</v>
+        <v>0.1587964296340942</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.004913266282528639</v>
+        <v>0.4390081763267517</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.004080809652805328</v>
+        <v>0.06805115193128586</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.002713024150580168</v>
+        <v>0.1298540681600571</v>
       </c>
       <c r="GC10" t="n">
-        <v>1.020074705593288e-05</v>
+        <v>0.144439309835434</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.001823735656216741</v>
+        <v>0.3139103353023529</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0007202335400506854</v>
+        <v>0.1190086379647255</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.002886604284867644</v>
+        <v>0.3243985176086426</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.001783833606168628</v>
+        <v>0.004875060170888901</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0002323990920558572</v>
+        <v>0.1111486479640007</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004967768676578999</v>
+        <v>0.583172082901001</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0003383657603990287</v>
+        <v>0.01273615658283234</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003032695036381483</v>
+        <v>0.07115250825881958</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0007044734666123986</v>
+        <v>0.03927266225218773</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00517844595015049</v>
+        <v>0.2865239381790161</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003203715896233916</v>
+        <v>0.007698066532611847</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00204882025718689</v>
+        <v>0.1119644716382027</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000427168735768646</v>
+        <v>0.003797083161771297</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001055819680914283</v>
+        <v>0.0443168506026268</v>
       </c>
       <c r="K11" t="n">
-        <v>0.004518892150372267</v>
+        <v>0.7098959684371948</v>
       </c>
       <c r="L11" t="n">
-        <v>5.413616599980742e-05</v>
+        <v>0.0022086501121521</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002441830700263381</v>
+        <v>0.1604174226522446</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0003105501236859709</v>
+        <v>0.1535471379756927</v>
       </c>
       <c r="O11" t="n">
-        <v>0.005211790557950735</v>
+        <v>0.2960976362228394</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0002105833118548617</v>
+        <v>0.114176906645298</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0008983684238046408</v>
+        <v>0.1003659069538116</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0002991127548739314</v>
+        <v>0.03913334757089615</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003126924275420606</v>
+        <v>0.03177161142230034</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0006461738958023489</v>
+        <v>0.09186487644910812</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0001409190444974229</v>
+        <v>0.0274478942155838</v>
       </c>
       <c r="V11" t="n">
-        <v>0.000502231705468148</v>
+        <v>0.133696436882019</v>
       </c>
       <c r="W11" t="n">
-        <v>3.399018169147894e-05</v>
+        <v>0.07387638092041016</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0001746930938679725</v>
+        <v>0.05931549146771431</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0004847975505981594</v>
+        <v>0.04350464046001434</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0003261833044234663</v>
+        <v>0.1622136533260345</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0003096787258982658</v>
+        <v>0.02684230357408524</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0001532568712718785</v>
+        <v>0.06523244082927704</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0006179550546221435</v>
+        <v>0.03585593029856682</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0001042909716488793</v>
+        <v>0.03378651663661003</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.000202367635210976</v>
+        <v>0.08632513135671616</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0002447977312840521</v>
+        <v>0.2375996112823486</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0003383909934200346</v>
+        <v>0.05558648705482483</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0003440260188654065</v>
+        <v>0.02501915581524372</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0006969051901251078</v>
+        <v>0.1784851849079132</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6.440110882977024e-05</v>
+        <v>0.03073128871619701</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0005027535371482372</v>
+        <v>0.01656047999858856</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0007087499252520502</v>
+        <v>0.08025969564914703</v>
       </c>
       <c r="AM11" t="n">
-        <v>7.649422332178801e-05</v>
+        <v>0.04388602077960968</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0003385501331649721</v>
+        <v>0.06668400764465332</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.00032455736072734</v>
+        <v>0.0005807371344417334</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0009111293475143611</v>
+        <v>0.07649744302034378</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.000372269656509161</v>
+        <v>0.07756496965885162</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0002863674890249968</v>
+        <v>0.1825477927923203</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0006130882538855076</v>
+        <v>0.0358252115547657</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0003663329989649355</v>
+        <v>0.04709206894040108</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.003140775021165609</v>
+        <v>0.5744887590408325</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0002355007163714617</v>
+        <v>0.005156286060810089</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0003120368928648531</v>
+        <v>0.01723486743867397</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0003478275611996651</v>
+        <v>0.1708994060754776</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.002676234114915133</v>
+        <v>0.2832019925117493</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0002010850002989173</v>
+        <v>0.007818592712283134</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.001056123292073607</v>
+        <v>0.009704379364848137</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0004725367471110076</v>
+        <v>0.01930968090891838</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0003747240989468992</v>
+        <v>0.01350557245314121</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.001205282984301448</v>
+        <v>0.01460747234523296</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.001578013063408434</v>
+        <v>0.03825419768691063</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.001226131687872112</v>
+        <v>0.09017054736614227</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.001518114935606718</v>
+        <v>0.03068111836910248</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001977124018594623</v>
+        <v>0.02773413434624672</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.632779695792124e-05</v>
+        <v>0.050995122641325</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0007664917502552271</v>
+        <v>0.07740498334169388</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0001589936582604423</v>
+        <v>0.04091465473175049</v>
       </c>
       <c r="BL11" t="n">
-        <v>4.928155249217525e-05</v>
+        <v>0.05656612291932106</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.001005623838864267</v>
+        <v>0.09556671231985092</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0005378421628847718</v>
+        <v>0.03136187046766281</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0006243209354579449</v>
+        <v>0.03524737060070038</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.835173316067085e-05</v>
+        <v>0.0920841172337532</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.000243386923102662</v>
+        <v>0.0050163883715868</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0005348414415493608</v>
+        <v>0.07265793532133102</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0003017080598510802</v>
+        <v>0.003978438675403595</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0003074767591897398</v>
+        <v>0.03645708784461021</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0002051927003776655</v>
+        <v>0.04709090292453766</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.001643458963371813</v>
+        <v>0.3838811218738556</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0005177113926038146</v>
+        <v>0.03168590739369392</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0002615969569887966</v>
+        <v>0.07000783830881119</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0001146180366049521</v>
+        <v>0.01813086494803429</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001207212917506695</v>
+        <v>0.1661975532770157</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0003873597597703338</v>
+        <v>0.07090139389038086</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0006550867110490799</v>
+        <v>0.1035826131701469</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0003881226584780961</v>
+        <v>0.006587551906704903</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.789267066167668e-05</v>
+        <v>0.02684364467859268</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0008731656707823277</v>
+        <v>0.168046623468399</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0005330834537744522</v>
+        <v>0.001106345327571034</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.000519380031619221</v>
+        <v>0.04636167362332344</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0002115810493705794</v>
+        <v>0.01001430116593838</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0008019364322535694</v>
+        <v>0.1051567196846008</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0002945793094113469</v>
+        <v>0.03564334288239479</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0002904115826822817</v>
+        <v>0.00321243517100811</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0003156090388074517</v>
+        <v>0.008637873455882072</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0006038019782863557</v>
+        <v>0.1365396827459335</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0003968884702771902</v>
+        <v>0.3262352049350739</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0002132508088834584</v>
+        <v>0.05781536549329758</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0006874068640172482</v>
+        <v>0.1790125221014023</v>
       </c>
       <c r="CQ11" t="n">
-        <v>8.271871774923056e-05</v>
+        <v>0.1278698295354843</v>
       </c>
       <c r="CR11" t="n">
-        <v>8.347931725438684e-06</v>
+        <v>0.1741672307252884</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0008352546719834208</v>
+        <v>0.05748317390680313</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0008619660511612892</v>
+        <v>0.05101507902145386</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0001418891188222915</v>
+        <v>0.001476447563618422</v>
       </c>
       <c r="CV11" t="n">
-        <v>8.69761934154667e-05</v>
+        <v>0.005970198661088943</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.000695710361469537</v>
+        <v>0.1642098724842072</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0005104776355437934</v>
+        <v>0.005567672196775675</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0007389851380139589</v>
+        <v>0.04705868288874626</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002181579184252769</v>
+        <v>0.004136286675930023</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0008304390939883888</v>
+        <v>0.09684655070304871</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0002602961321827024</v>
+        <v>0.0146761741489172</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0005324828671291471</v>
+        <v>0.0005903732962906361</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0001879077608464286</v>
+        <v>0.009076789021492004</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0005955984233878553</v>
+        <v>0.01447767578065395</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0007527697598561645</v>
+        <v>0.1066308617591858</v>
       </c>
       <c r="DG11" t="n">
-        <v>5.974710802547634e-05</v>
+        <v>0.06451340764760971</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.001467964728362858</v>
+        <v>0.04963839799165726</v>
       </c>
       <c r="DI11" t="n">
-        <v>5.465354479383677e-05</v>
+        <v>0.1702721565961838</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0001641873823245987</v>
+        <v>0.0144939785823226</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0005762926884926856</v>
+        <v>0.08987453579902649</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.001226416090503335</v>
+        <v>0.01920146495103836</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0007429518736898899</v>
+        <v>0.03004207089543343</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0002560014836490154</v>
+        <v>0.06568273156881332</v>
       </c>
       <c r="DO11" t="n">
-        <v>8.62637534737587e-08</v>
+        <v>0.1135318353772163</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0004651244671549648</v>
+        <v>0.03902707248926163</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0004688245244324207</v>
+        <v>0.08416945487260818</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0003687701828312129</v>
+        <v>0.04887578263878822</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0005000546807423234</v>
+        <v>0.0533580370247364</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0002517387038096786</v>
+        <v>0.03256839513778687</v>
       </c>
       <c r="DU11" t="n">
-        <v>3.188270784448832e-05</v>
+        <v>0.1221355274319649</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0005561478319577873</v>
+        <v>0.01103889103978872</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.000209439531317912</v>
+        <v>0.0957210436463356</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0005433417391031981</v>
+        <v>0.009129747748374939</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0005657065194100142</v>
+        <v>0.03659776598215103</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0006102314218878746</v>
+        <v>0.004860509186983109</v>
       </c>
       <c r="EA11" t="n">
-        <v>5.414511542767286e-05</v>
+        <v>0.05774098634719849</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0001273385278182104</v>
+        <v>0.05844580382108688</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.238495653728023e-05</v>
+        <v>0.007239954546093941</v>
       </c>
       <c r="ED11" t="n">
-        <v>8.819073991617188e-05</v>
+        <v>0.006832518614828587</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0003969650133512914</v>
+        <v>0.06837672740221024</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0003613898879848421</v>
+        <v>0.0005766265094280243</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.00072232645470649</v>
+        <v>0.08422158658504486</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.000383815640816465</v>
+        <v>0.007688869722187519</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0001367327786283568</v>
+        <v>0.01709161698818207</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0002071508060907945</v>
+        <v>0.05119097232818604</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0007251693168655038</v>
+        <v>0.05316068977117538</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0005209033843129873</v>
+        <v>0.00461288820952177</v>
       </c>
       <c r="EM11" t="n">
-        <v>6.00659623160027e-05</v>
+        <v>0.05454892292618752</v>
       </c>
       <c r="EN11" t="n">
-        <v>2.906526788137853e-06</v>
+        <v>0.002682185731828213</v>
       </c>
       <c r="EO11" t="n">
-        <v>7.477417238987982e-05</v>
+        <v>0.008747247979044914</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0004516678163781762</v>
+        <v>0.07607423514127731</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0005952842766419053</v>
+        <v>0.03188605234026909</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0006503678159788251</v>
+        <v>0.04270375519990921</v>
       </c>
       <c r="ES11" t="n">
-        <v>1.026673999149352e-06</v>
+        <v>0.05854779481887817</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.000187156445463188</v>
+        <v>0.03211018443107605</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0001530516310594976</v>
+        <v>0.01840838417410851</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.0008817645139060915</v>
+        <v>0.02079591527581215</v>
       </c>
       <c r="EW11" t="n">
-        <v>6.419359124265611e-05</v>
+        <v>0.04211778938770294</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0001467500987928361</v>
+        <v>0.02015295065939426</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0007164460839703679</v>
+        <v>0.1822786331176758</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0003635013126768172</v>
+        <v>0.00135213672183454</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0004876130842603743</v>
+        <v>0.04516665637493134</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.000201707414817065</v>
+        <v>0.01571779698133469</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0007895848830230534</v>
+        <v>0.09826874732971191</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0004258113331161439</v>
+        <v>0.04947086796164513</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.000285764952423051</v>
+        <v>0.0149043332785368</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0004300661967135966</v>
+        <v>0.01618871465325356</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0001433791185263544</v>
+        <v>0.03951876983046532</v>
       </c>
       <c r="FH11" t="n">
-        <v>4.357129364507273e-05</v>
+        <v>0.158036857843399</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0005327622056938708</v>
+        <v>0.01829141937196255</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.001154670026153326</v>
+        <v>0.1100426018238068</v>
       </c>
       <c r="FK11" t="n">
-        <v>4.861881461692974e-05</v>
+        <v>0.06403549015522003</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0007881324272602797</v>
+        <v>0.07730762660503387</v>
       </c>
       <c r="FM11" t="n">
-        <v>2.900284016504884e-06</v>
+        <v>0.05748721212148666</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0001668839831836522</v>
+        <v>0.1709606945514679</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.000137298135086894</v>
+        <v>0.01190703548491001</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.0002203737676609308</v>
+        <v>0.02156034484505653</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0007544406689703465</v>
+        <v>0.1680166274309158</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0002527547476347536</v>
+        <v>0.006682321429252625</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0005587585037574172</v>
+        <v>0.2523631751537323</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0009966096840798855</v>
+        <v>0.01779884099960327</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0008552205981686711</v>
+        <v>0.1014323607087135</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0001066951517714188</v>
+        <v>0.07992637157440186</v>
       </c>
       <c r="FW11" t="n">
-        <v>5.770373536506668e-05</v>
+        <v>0.06212280690670013</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0003168726398143917</v>
+        <v>0.02806512266397476</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.0009652373264543712</v>
+        <v>0.1101662069559097</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0002652137191034853</v>
+        <v>0.0810837596654892</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0001784787164069712</v>
+        <v>0.05894476547837257</v>
       </c>
       <c r="GB11" t="n">
-        <v>4.879594780504704e-05</v>
+        <v>0.02832650393247604</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0003966608783230186</v>
+        <v>0.02315685153007507</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0008307653479278088</v>
+        <v>0.01456988416612148</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.001853122026659548</v>
+        <v>0.09200477600097656</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.000382137339329347</v>
+        <v>0.02448387444019318</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0006569940596818924</v>
+        <v>0.08594109117984772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.005510426592081785</v>
+        <v>0.1417607516050339</v>
       </c>
       <c r="B12" t="n">
-        <v>0.09329134225845337</v>
+        <v>0.09999470412731171</v>
       </c>
       <c r="C12" t="n">
-        <v>0.009947018697857857</v>
+        <v>0.111603632569313</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05042727291584015</v>
+        <v>0.374785840511322</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01108228415250778</v>
+        <v>0.04522346332669258</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004030821844935417</v>
+        <v>0.3232616186141968</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00138486863579601</v>
+        <v>0.2196197658777237</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006479438859969378</v>
+        <v>0.1815273463726044</v>
       </c>
       <c r="I12" t="n">
-        <v>0.005041603930294514</v>
+        <v>0.08326693624258041</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004976511932909489</v>
+        <v>0.1299131065607071</v>
       </c>
       <c r="K12" t="n">
-        <v>0.07748384773731232</v>
+        <v>0.02214233204722404</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0005697903106920421</v>
+        <v>0.1262935847043991</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04621487855911255</v>
+        <v>0.5097429752349854</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02003030478954315</v>
+        <v>0.01266801729798317</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01055300980806351</v>
+        <v>0.3092093169689178</v>
       </c>
       <c r="P12" t="n">
-        <v>0.006472495384514332</v>
+        <v>0.2295832335948944</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.009021233767271042</v>
+        <v>0.1078324317932129</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001315909554250538</v>
+        <v>0.1447771191596985</v>
       </c>
       <c r="S12" t="n">
-        <v>0.004385418258607388</v>
+        <v>0.00260107615031302</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01182097382843494</v>
+        <v>0.03227492421865463</v>
       </c>
       <c r="U12" t="n">
-        <v>0.002544512739405036</v>
+        <v>0.004541082307696342</v>
       </c>
       <c r="V12" t="n">
-        <v>0.006165503524243832</v>
+        <v>0.0259909275919199</v>
       </c>
       <c r="W12" t="n">
-        <v>0.005287046078592539</v>
+        <v>0.02741668373346329</v>
       </c>
       <c r="X12" t="n">
-        <v>0.007279869168996811</v>
+        <v>0.1106375232338905</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.009677874855697155</v>
+        <v>0.01389612164348364</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.006829326041042805</v>
+        <v>0.01887444034218788</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.007494539022445679</v>
+        <v>0.02255813404917717</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01341233775019646</v>
+        <v>0.02333242632448673</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01808596029877663</v>
+        <v>0.01631986163556576</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.001432230114005506</v>
+        <v>0.03959313035011292</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.001674781087785959</v>
+        <v>0.05658891424536705</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.004028851632028818</v>
+        <v>0.04080145806074142</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001570061431266367</v>
+        <v>0.1548802256584167</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.002716502174735069</v>
+        <v>0.06527181714773178</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.003171564545482397</v>
+        <v>0.1095161065459251</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.001606925390660763</v>
+        <v>0.05980153754353523</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.004018381237983704</v>
+        <v>0.03663670271635056</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.009336559101939201</v>
+        <v>0.06561914086341858</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.002751190215349197</v>
+        <v>0.004025986418128014</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.001723401248455048</v>
+        <v>0.04035298526287079</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.01085888873785734</v>
+        <v>0.1088101118803024</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.008360942825675011</v>
+        <v>0.06262435019016266</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.004526000004261732</v>
+        <v>0.06777690351009369</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.00238511641509831</v>
+        <v>0.08469822257757187</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.001692310906946659</v>
+        <v>0.02371607720851898</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.01194494031369686</v>
+        <v>0.1174119263887405</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.06366920471191406</v>
+        <v>0.1295151859521866</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.001106286188587546</v>
+        <v>0.1271931529045105</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02119720540940762</v>
+        <v>0.167065292596817</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.008561752736568451</v>
+        <v>0.1689780056476593</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.001578460680320859</v>
+        <v>0.2072282284498215</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.007606068160384893</v>
+        <v>0.01408258825540543</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.001246029627509415</v>
+        <v>0.05509219691157341</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0005316140595823526</v>
+        <v>0.1296632587909698</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.006323751993477345</v>
+        <v>0.0327216312289238</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02106619812548161</v>
+        <v>0.08898992836475372</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.01823469623923302</v>
+        <v>0.059386245906353</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.005276470445096493</v>
+        <v>0.004662411287426949</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01410461775958538</v>
+        <v>0.06585635244846344</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.009308791719377041</v>
+        <v>0.007696716114878654</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.005025764927268028</v>
+        <v>0.06994012743234634</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.009741204790771008</v>
+        <v>0.007673713844269514</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.003786545712500811</v>
+        <v>0.04277800768613815</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.008870159275829792</v>
+        <v>0.003691130317747593</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01688456907868385</v>
+        <v>0.05388246476650238</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.01345579512417316</v>
+        <v>0.04244682937860489</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0002718750620260835</v>
+        <v>0.05051345005631447</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01360259857028723</v>
+        <v>0.0779939591884613</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.007101551629602909</v>
+        <v>0.06837227940559387</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.003480667714029551</v>
+        <v>0.04912964999675751</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.003462575376033783</v>
+        <v>0.03118949569761753</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.004636130295693874</v>
+        <v>0.01168022397905588</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.007551637012511492</v>
+        <v>0.06437188386917114</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0341658927500248</v>
+        <v>0.1199833452701569</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.01096842903643847</v>
+        <v>0.03039751388132572</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01442340202629566</v>
+        <v>0.1427256762981415</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.005001981277018785</v>
+        <v>0.01613422855734825</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.008469297550618649</v>
+        <v>0.1341822445392609</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.003752910764887929</v>
+        <v>0.02711490914225578</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.003258571494370699</v>
+        <v>0.01480793487280607</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.006939182989299297</v>
+        <v>0.02232975512742996</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.001366201904602349</v>
+        <v>0.07290327548980713</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.01437871810048819</v>
+        <v>0.02900315262377262</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.005447277799248695</v>
+        <v>0.04116873815655708</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.004781662952154875</v>
+        <v>0.111311674118042</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.004711605142802</v>
+        <v>0.01323592662811279</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0009527226211503148</v>
+        <v>0.03653277456760406</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0027666836977005</v>
+        <v>0.001006369013339281</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0006274195038713515</v>
+        <v>0.06897541135549545</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.002447302918881178</v>
+        <v>0.02488314360380173</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.02223973907530308</v>
+        <v>0.1005328819155693</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.01299038343131542</v>
+        <v>0.05635862424969673</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0001699734712019563</v>
+        <v>0.1029594838619232</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.01339750178158283</v>
+        <v>0.1076123341917992</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01563718728721142</v>
+        <v>0.09115511178970337</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.006367440335452557</v>
+        <v>0.1007230281829834</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.008797099813818932</v>
+        <v>0.06788885593414307</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.01704391837120056</v>
+        <v>0.01932886615395546</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.992413308471441e-05</v>
+        <v>0.003307133913040161</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.000130677450215444</v>
+        <v>0.07311545312404633</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.01333670504391193</v>
+        <v>0.02312036976218224</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.006618223153054714</v>
+        <v>0.05039868503808975</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.008352503180503845</v>
+        <v>0.1243813335895538</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.005336293019354343</v>
+        <v>0.02058296278119087</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.001825136132538319</v>
+        <v>0.03989750146865845</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.001690038247033954</v>
+        <v>0.009145843796432018</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.00110452645458281</v>
+        <v>0.05063257366418839</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0007873032009229064</v>
+        <v>0.03075255639851093</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.01121767051517963</v>
+        <v>0.09175923466682434</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.01044500339776278</v>
+        <v>0.06194552779197693</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.003189325099810958</v>
+        <v>0.01098483055830002</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03043602965772152</v>
+        <v>0.1153950244188309</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.005430189892649651</v>
+        <v>0.04193641990423203</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.002094464609399438</v>
+        <v>0.2152878046035767</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.004681095946580172</v>
+        <v>0.00242728553712368</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01087282132357359</v>
+        <v>0.1863301545381546</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.004160908982157707</v>
+        <v>0.07455907762050629</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.005294010043144226</v>
+        <v>0.04071356728672981</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.007048522587865591</v>
+        <v>0.05623659864068031</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.00670186709612608</v>
+        <v>0.004590442404150963</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.006958747748285532</v>
+        <v>0.0001589320600032806</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01185918506234884</v>
+        <v>0.002142777666449547</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.003915718756616116</v>
+        <v>0.07298578321933746</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.004325337707996368</v>
+        <v>0.04190345108509064</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.004044919274747372</v>
+        <v>0.01552875153720379</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0009409270714968443</v>
+        <v>0.1199103444814682</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.005952424835413694</v>
+        <v>0.02127962745726109</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01817683316767216</v>
+        <v>0.04579957574605942</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0003704591654241085</v>
+        <v>0.127578005194664</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.005325073841959238</v>
+        <v>0.02041825652122498</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01354740746319294</v>
+        <v>0.0438142716884613</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.005233506672084332</v>
+        <v>0.02348688989877701</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.002734176814556122</v>
+        <v>0.05551799759268761</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0004377456207294017</v>
+        <v>0.06416521221399307</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.00236194278113544</v>
+        <v>0.1183217316865921</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0003473362885415554</v>
+        <v>0.06576083600521088</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.007652141619473696</v>
+        <v>0.03156373649835587</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.004250180907547474</v>
+        <v>0.02057956531643867</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.008549162186682224</v>
+        <v>0.1177757382392883</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.005740328691899776</v>
+        <v>0.007624432444572449</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.001358168898150325</v>
+        <v>0.01985909231007099</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.001705510658212006</v>
+        <v>0.0009741373360157013</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.002936766482889652</v>
+        <v>0.0388774462044239</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0006523196934722364</v>
+        <v>0.03625736385583878</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.005699157249182463</v>
+        <v>0.08973079174757004</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.009747969917953014</v>
+        <v>0.04138142615556717</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.009169307537376881</v>
+        <v>0.0678219199180603</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.003807343076914549</v>
+        <v>0.1381128579378128</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.006764834746718407</v>
+        <v>0.0007744645699858665</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.00582722807303071</v>
+        <v>0.06512556225061417</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.004157469142228365</v>
+        <v>0.07499489188194275</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.007377252448350191</v>
+        <v>0.03558467328548431</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.00130371970590204</v>
+        <v>0.1279259920120239</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.003294242080301046</v>
+        <v>0.08234977722167969</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.01343061495572329</v>
+        <v>0.04392822459340096</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.004251564387232065</v>
+        <v>0.02751588821411133</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.005719059146940708</v>
+        <v>0.1309428364038467</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.002344839042052627</v>
+        <v>0.0107833044603467</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.003480829298496246</v>
+        <v>0.05506042763590813</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.002922152867540717</v>
+        <v>0.01539184711873531</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0007329400395974517</v>
+        <v>0.05455927550792694</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.002624370157718658</v>
+        <v>0.01961348950862885</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.001774474047124386</v>
+        <v>0.003080879803746939</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.008504859171807766</v>
+        <v>0.007719074375927448</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.00167634675744921</v>
+        <v>0.08498885482549667</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.00999092310667038</v>
+        <v>0.04900256171822548</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.006788793485611677</v>
+        <v>0.05769973248243332</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.008886865340173244</v>
+        <v>0.09139568358659744</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.008244297467172146</v>
+        <v>0.05085060000419617</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0006642674561589956</v>
+        <v>0.0929010808467865</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.004067531786859035</v>
+        <v>0.05671232938766479</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.004917293787002563</v>
+        <v>0.01523739937692881</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.008686980232596397</v>
+        <v>0.04556457325816154</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.005340005736798048</v>
+        <v>0.04558680206537247</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.006890604272484779</v>
+        <v>0.02962545864284039</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.003124730195850134</v>
+        <v>0.002433454617857933</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.002313935663551092</v>
+        <v>0.02205951139330864</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.003345965640619397</v>
+        <v>0.04951810836791992</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0007079248898662627</v>
+        <v>0.223572313785553</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.004049004055559635</v>
+        <v>0.03568993508815765</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.01102720480412245</v>
+        <v>0.03884890675544739</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.005179624073207378</v>
+        <v>0.001501521095633507</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.00177528930362314</v>
+        <v>0.09398993849754333</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0005802009254693985</v>
+        <v>0.1359528601169586</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.00167127326130867</v>
+        <v>0.1522872000932693</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.01191873382776976</v>
+        <v>0.09013085067272186</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0152111891657114</v>
+        <v>0.1018427312374115</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.001198180485516787</v>
+        <v>0.007776771672070026</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0001345678465440869</v>
+        <v>0.1047119647264481</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01050173491239548</v>
+        <v>0.05821770057082176</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0007564560510218143</v>
+        <v>0.01292035169899464</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002514334861189127</v>
+        <v>0.02719220705330372</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006291531026363373</v>
+        <v>0.1585304290056229</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001747955684550107</v>
+        <v>0.05856043100357056</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002598877297714353</v>
+        <v>0.03389575332403183</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001549510518088937</v>
+        <v>0.07532310485839844</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001066891360096633</v>
+        <v>0.0104479705914855</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003503976913634688</v>
+        <v>0.02182642929255962</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009214379824697971</v>
+        <v>0.02188721671700478</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0008370316354557872</v>
+        <v>0.04373028501868248</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003069570288062096</v>
+        <v>0.04260651767253876</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002464102115482092</v>
+        <v>0.2151909023523331</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0023857899941504</v>
+        <v>0.008412085473537445</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0004881910281255841</v>
+        <v>0.03459146618843079</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000277721497695893</v>
+        <v>0.05044511333107948</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0012892090016976</v>
+        <v>0.05177867412567139</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0007166711729951203</v>
+        <v>0.01976031623780727</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001464126631617546</v>
+        <v>0.0006048749200999737</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0022189577575773</v>
+        <v>0.003868402913212776</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001025112578645349</v>
+        <v>0.003750865114852786</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0001962576352525502</v>
+        <v>0.01648003235459328</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0009395908564329147</v>
+        <v>0.01894580759108067</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003293401678092778</v>
+        <v>0.07668088376522064</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.469993528909981e-05</v>
+        <v>0.00758830551058054</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001664177631027997</v>
+        <v>0.0005954992957413197</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0003784531727433205</v>
+        <v>0.003914563450962305</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001051105558872223</v>
+        <v>0.0123234186321497</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.002359914127737284</v>
+        <v>0.007431014440953732</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0006234904285520315</v>
+        <v>0.005363437347114086</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0005378745263442397</v>
+        <v>0.02044666185975075</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001049193437211215</v>
+        <v>0.08616778254508972</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0007288622437044978</v>
+        <v>0.05819376558065414</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0004736215341836214</v>
+        <v>0.03259087726473808</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0008894946076907218</v>
+        <v>0.0413176454603672</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0006562877679243684</v>
+        <v>0.04318778961896896</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.001467940048314631</v>
+        <v>0.008667053654789925</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.080065991729498e-05</v>
+        <v>0.01987921074032784</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0004609531897585839</v>
+        <v>0.03093722648918629</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001056008390150964</v>
+        <v>0.0463312566280365</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001367094460874796</v>
+        <v>0.02876627817749977</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0005880944081582129</v>
+        <v>0.02241835370659828</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.001289719948545098</v>
+        <v>0.05262208357453346</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.001265030237846076</v>
+        <v>0.02053850702941418</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0005803233361802995</v>
+        <v>0.0008759542251937091</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.006621968001127243</v>
+        <v>0.02152683399617672</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.002152825240045786</v>
+        <v>0.00502723827958107</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.002807668410241604</v>
+        <v>0.009328450076282024</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.003620513714849949</v>
+        <v>0.1047991067171097</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.002346037654206157</v>
+        <v>0.01956672221422195</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0005687958328053355</v>
+        <v>0.03266074135899544</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0005854620831087232</v>
+        <v>0.03452387824654579</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.002310347277671099</v>
+        <v>0.01901428401470184</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0009105396457016468</v>
+        <v>0.03353453800082207</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.004249491728842258</v>
+        <v>0.06224073469638824</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.005419149063527584</v>
+        <v>0.006706104148179293</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0004468848346732557</v>
+        <v>0.004603015724569559</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0004702541045844555</v>
+        <v>0.05980083346366882</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001683171256445348</v>
+        <v>0.08877326548099518</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.659108425490558e-05</v>
+        <v>0.02417834848165512</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0005397822242230177</v>
+        <v>0.06254231184720993</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002560549648478627</v>
+        <v>0.007800305727869272</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.001679806970059872</v>
+        <v>0.06108075752854347</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0005769968265667558</v>
+        <v>0.0004808660596609116</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.002488788682967424</v>
+        <v>0.03274263441562653</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0004808885860256851</v>
+        <v>0.02294383198022842</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0005625608027912676</v>
+        <v>0.01847446523606777</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0005804807879030704</v>
+        <v>0.03268834948539734</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0009372135391458869</v>
+        <v>0.005205401219427586</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001105583622120321</v>
+        <v>0.0002542457077652216</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0004598313244059682</v>
+        <v>0.00534520111978054</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0008401621598750353</v>
+        <v>0.01110157091170549</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.002869532443583012</v>
+        <v>0.00977653544396162</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0001035601308103651</v>
+        <v>0.03352979943156242</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.001123433234170079</v>
+        <v>0.002397247590124607</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.001537587959319353</v>
+        <v>0.1058908551931381</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0002346262917853892</v>
+        <v>0.02746975421905518</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0003938801819458604</v>
+        <v>0.04133550450205803</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0005229492671787739</v>
+        <v>0.01850795745849609</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.001637814682908356</v>
+        <v>0.01444102823734283</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0004193983040750027</v>
+        <v>0.02701673842966557</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.002023672219365835</v>
+        <v>0.01338578388094902</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.001502062194049358</v>
+        <v>0.003738071769475937</v>
       </c>
       <c r="CF13" t="n">
-        <v>5.420617526397109e-06</v>
+        <v>0.007007105275988579</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0005768678965978324</v>
+        <v>0.05283096432685852</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0001066087206709199</v>
+        <v>0.01032963860780001</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.001405467046424747</v>
+        <v>0.0227360725402832</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.576404949650168e-05</v>
+        <v>0.001627112505957484</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.001214729738421738</v>
+        <v>0.01155365444719791</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0002063660213025287</v>
+        <v>0.01424742117524147</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.002516514156013727</v>
+        <v>0.01485868915915489</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.000830874138046056</v>
+        <v>0.0292494036257267</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0001003705838229507</v>
+        <v>0.02533983439207077</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.002274278784170747</v>
+        <v>0.05893482267856598</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.003113775048404932</v>
+        <v>0.0794798880815506</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0007869007531553507</v>
+        <v>0.0141779612749815</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.002240808680653572</v>
+        <v>0.02323123067617416</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.003861335106194019</v>
+        <v>0.01099754963070154</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0009505163179710507</v>
+        <v>0.07610529661178589</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001506694359704852</v>
+        <v>0.01390649192035198</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.00176537421066314</v>
+        <v>0.002709319349378347</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0001734806864988059</v>
+        <v>0.004966817796230316</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0007190221804194152</v>
+        <v>0.05390411987900734</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0001112302634282969</v>
+        <v>0.008344340138137341</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.00106937694363296</v>
+        <v>0.02351103723049164</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001792673720046878</v>
+        <v>0.004412560723721981</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0009158776374533772</v>
+        <v>0.00967030506581068</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.000179326074430719</v>
+        <v>0.006022418383508921</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001201523235067725</v>
+        <v>0.01618528366088867</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.002134585753083229</v>
+        <v>0.02418613247573376</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.002912910189479589</v>
+        <v>0.01544284820556641</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.00364292087033391</v>
+        <v>0.0533289797604084</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0005140498396940529</v>
+        <v>0.01296501886099577</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0006665245746262372</v>
+        <v>0.005319499410688877</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001025411416776478</v>
+        <v>0.02749679237604141</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.004379014018923044</v>
+        <v>0.1185853555798531</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0008872740436345339</v>
+        <v>0.02118377387523651</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0009116295841522515</v>
+        <v>0.02029574289917946</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0002309531555511057</v>
+        <v>0.01761962845921516</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0007855809526517987</v>
+        <v>0.03484310954809189</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0009535087738186121</v>
+        <v>0.005863189697265625</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.00235738349147141</v>
+        <v>0.01057039760053158</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0008419759687967598</v>
+        <v>0.01595141738653183</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0008136490359902382</v>
+        <v>0.008118324913084507</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0003393536317162216</v>
+        <v>0.00986192375421524</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.001362241921015084</v>
+        <v>0.07821699976921082</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.00203878921456635</v>
+        <v>0.01427276711910963</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001487813657149673</v>
+        <v>0.00299902493134141</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.000370398658560589</v>
+        <v>0.04673361778259277</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0009201281936839223</v>
+        <v>0.00471828505396843</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.001044851611368358</v>
+        <v>0.01449251268059015</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0006370110204443336</v>
+        <v>0.007002671714872122</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0003040885785594583</v>
+        <v>0.009626977145671844</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0001836243900470436</v>
+        <v>0.06835091859102249</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0006637233309447765</v>
+        <v>0.05144289135932922</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0019664925057441</v>
+        <v>0.02199330367147923</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.002301768166944385</v>
+        <v>0.01040357816964388</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.001227330649271607</v>
+        <v>0.006680313032120466</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.00244476180523634</v>
+        <v>0.06382187455892563</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.002473931992426515</v>
+        <v>0.005821263417601585</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0005324967205524445</v>
+        <v>0.01106972806155682</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001218881370732561</v>
+        <v>0.008386525325477123</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0002504348813090473</v>
+        <v>0.01156210340559483</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0002731033600866795</v>
+        <v>0.01962954364717007</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0001233993680216372</v>
+        <v>0.001024647615849972</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.003386748488992453</v>
+        <v>0.006325792521238327</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0007054522284306586</v>
+        <v>0.002023342996835709</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0001350081292912364</v>
+        <v>0.07300590723752975</v>
       </c>
       <c r="ES13" t="n">
-        <v>9.860075078904629e-05</v>
+        <v>0.01368826627731323</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001453239237889647</v>
+        <v>0.0573403611779213</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0009384283912368119</v>
+        <v>0.02382337860763073</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0004458822368178517</v>
+        <v>0.002472091466188431</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.00206280592828989</v>
+        <v>0.02926101535558701</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001645014039240777</v>
+        <v>0.0139476777985692</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.001769150258041918</v>
+        <v>0.001865445170551538</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0003448915667831898</v>
+        <v>0.007271669339388609</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0006347264861688018</v>
+        <v>0.06517188251018524</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001528508437331766</v>
+        <v>0.01229891926050186</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.001107720891013741</v>
+        <v>0.002295392565429211</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0002022648986894637</v>
+        <v>0.00531322043389082</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.001024747616611421</v>
+        <v>0.01489893533289433</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0002846250717993826</v>
+        <v>0.0003889775834977627</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0002588019124232233</v>
+        <v>0.0006351761985570192</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.002448909683153033</v>
+        <v>0.007499315775930882</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.002487952820956707</v>
+        <v>0.01297508366405964</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0004698792472481728</v>
+        <v>0.02172963693737984</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0009604080696590245</v>
+        <v>0.03414147719740868</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.00254782335832715</v>
+        <v>0.006871504709124565</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.001312646549195051</v>
+        <v>0.02852293290197849</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0006549263489432633</v>
+        <v>0.01693727448582649</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0008791880682110786</v>
+        <v>0.03251650929450989</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001450680661946535</v>
+        <v>0.002283507026731968</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.001101318397559226</v>
+        <v>0.02885962463915348</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.001704101450741291</v>
+        <v>0.01721134409308434</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.001851035747677088</v>
+        <v>0.05193591490387917</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.002833271631971002</v>
+        <v>0.0784701481461525</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.002354091266170144</v>
+        <v>0.03282900527119637</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.001280519179999828</v>
+        <v>0.02463512308895588</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0003927809884771705</v>
+        <v>0.02411013841629028</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0005421803798526525</v>
+        <v>0.01692091673612595</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.00100234616547823</v>
+        <v>0.0007491549476981163</v>
       </c>
       <c r="FZ13" t="n">
-        <v>1.22649798868224e-05</v>
+        <v>0.01803221367299557</v>
       </c>
       <c r="GA13" t="n">
-        <v>5.170120857656002e-06</v>
+        <v>0.006909850519150496</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0001564878039062023</v>
+        <v>0.07925520092248917</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.001227733679115772</v>
+        <v>0.03233537822961807</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0002073278010357171</v>
+        <v>0.02689663507044315</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0009955022251233459</v>
+        <v>0.05445998907089233</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0004263925948180258</v>
+        <v>0.004223959986120462</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.001087187556549907</v>
+        <v>0.01241973601281643</v>
       </c>
     </row>
     <row r="14">
@@ -8965,571 +8965,571 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2.934546827759732e-09</v>
+        <v>8.363091469343331e-11</v>
       </c>
       <c r="B16" t="n">
-        <v>2.484724603846189e-08</v>
+        <v>2.520209041456667e-10</v>
       </c>
       <c r="C16" t="n">
-        <v>3.654305080758036e-09</v>
+        <v>4.449280874285755e-11</v>
       </c>
       <c r="D16" t="n">
-        <v>4.965550459701262e-08</v>
+        <v>3.795259106986748e-10</v>
       </c>
       <c r="E16" t="n">
-        <v>9.318380733702725e-09</v>
+        <v>2.787412245464083e-10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.053773411920702e-08</v>
+        <v>2.786281483313502e-10</v>
       </c>
       <c r="G16" t="n">
-        <v>1.115397640916171e-08</v>
+        <v>2.420330880159582e-10</v>
       </c>
       <c r="H16" t="n">
-        <v>2.112722441438564e-08</v>
+        <v>4.036358469683421e-10</v>
       </c>
       <c r="I16" t="n">
-        <v>1.477547506567589e-08</v>
+        <v>2.514741193060388e-10</v>
       </c>
       <c r="J16" t="n">
-        <v>2.179082470021854e-09</v>
+        <v>2.800653459145153e-11</v>
       </c>
       <c r="K16" t="n">
-        <v>2.177339375464271e-08</v>
+        <v>1.494186718797863e-10</v>
       </c>
       <c r="L16" t="n">
-        <v>3.351003474705294e-09</v>
+        <v>2.828499240381532e-11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.855500369491892e-08</v>
+        <v>5.71677816196825e-10</v>
       </c>
       <c r="N16" t="n">
-        <v>1.745809186104452e-08</v>
+        <v>4.652478124977932e-10</v>
       </c>
       <c r="O16" t="n">
-        <v>1.144837202815552e-08</v>
+        <v>2.8606669810749e-10</v>
       </c>
       <c r="P16" t="n">
-        <v>3.871361453633426e-09</v>
+        <v>2.771199936191238e-10</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.294340634672153e-09</v>
+        <v>3.811000681697152e-10</v>
       </c>
       <c r="R16" t="n">
-        <v>3.312181640069412e-10</v>
+        <v>2.325250547663416e-10</v>
       </c>
       <c r="S16" t="n">
-        <v>5.793754920269123e-10</v>
+        <v>2.608440199947104e-11</v>
       </c>
       <c r="T16" t="n">
-        <v>1.122864823344116e-08</v>
+        <v>1.041719072114589e-10</v>
       </c>
       <c r="U16" t="n">
-        <v>9.890246399635316e-10</v>
+        <v>1.489737638804556e-10</v>
       </c>
       <c r="V16" t="n">
-        <v>3.717997021368546e-09</v>
+        <v>4.602190503688597e-11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.794469639548879e-08</v>
+        <v>1.035811089677985e-10</v>
       </c>
       <c r="X16" t="n">
-        <v>7.41405425941366e-09</v>
+        <v>1.00753060408576e-11</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15265121891639e-08</v>
+        <v>6.726926654598842e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.505144536257831e-09</v>
+        <v>9.459970307101884e-11</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.326298981751961e-08</v>
+        <v>6.384800674275048e-12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.521651071811903e-08</v>
+        <v>1.39638049387325e-11</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.07661603468523e-08</v>
+        <v>1.287492890078568e-10</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.257094606188502e-08</v>
+        <v>2.41997359651247e-11</v>
       </c>
       <c r="AE16" t="n">
-        <v>9.948091239664336e-10</v>
+        <v>1.161399448834644e-10</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.720969922125448e-09</v>
+        <v>8.266887174812609e-11</v>
       </c>
       <c r="AG16" t="n">
-        <v>6.890274573123634e-09</v>
+        <v>1.044617864431885e-10</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.310488872974247e-08</v>
+        <v>8.632091569316103e-11</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.706243033642977e-09</v>
+        <v>1.868440541175076e-10</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.381240316040589e-09</v>
+        <v>4.768438074953529e-11</v>
       </c>
       <c r="AK16" t="n">
-        <v>7.378169630811726e-09</v>
+        <v>9.947695445156057e-12</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.972078914202484e-09</v>
+        <v>7.210047142658382e-11</v>
       </c>
       <c r="AM16" t="n">
-        <v>3.796994718641145e-09</v>
+        <v>1.881948208382056e-10</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.172131668449651e-09</v>
+        <v>1.168471014389993e-10</v>
       </c>
       <c r="AO16" t="n">
-        <v>9.010433510425742e-10</v>
+        <v>8.951497182385637e-11</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.244665146619809e-09</v>
+        <v>1.241470988511129e-11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.189673870527486e-08</v>
+        <v>3.585760161017859e-11</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.784819899825379e-09</v>
+        <v>5.130396454888775e-11</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.392722020516658e-09</v>
+        <v>3.466747722224994e-11</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.783443253662199e-09</v>
+        <v>2.248231184553973e-10</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.887214828855122e-08</v>
+        <v>2.552948408229838e-10</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.943337016451778e-09</v>
+        <v>1.984786779374303e-10</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.194813551019251e-09</v>
+        <v>6.82124218220892e-11</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.085078053606139e-09</v>
+        <v>4.511858109346178e-10</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.124437876143247e-09</v>
+        <v>2.815337685202479e-10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.360300482313505e-09</v>
+        <v>9.192147043535215e-11</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.751110781522129e-09</v>
+        <v>5.852515694293459e-11</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.373732099769654e-09</v>
+        <v>6.039267003155047e-11</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.325830911724779e-08</v>
+        <v>5.465033980911471e-11</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.368589046066518e-09</v>
+        <v>1.827002438226089e-10</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.334307383644045e-09</v>
+        <v>7.828215159433327e-11</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.510501471268526e-09</v>
+        <v>1.979548330810488e-10</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.818901829153674e-08</v>
+        <v>2.531136689132296e-10</v>
       </c>
       <c r="BH16" t="n">
-        <v>1.889418754785765e-08</v>
+        <v>1.064463031608121e-10</v>
       </c>
       <c r="BI16" t="n">
-        <v>6.769102611769995e-09</v>
+        <v>2.564778597835549e-11</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.463218168851199e-08</v>
+        <v>2.182254515981086e-10</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.17794929366255e-09</v>
+        <v>1.224800955101912e-10</v>
       </c>
       <c r="BL16" t="n">
-        <v>7.117919587074084e-09</v>
+        <v>5.524082233310246e-11</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.450815241507371e-09</v>
+        <v>2.427383571923514e-10</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.462522935038237e-09</v>
+        <v>7.909941451833546e-11</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.053561504704703e-08</v>
+        <v>1.476699179603358e-10</v>
       </c>
       <c r="BP16" t="n">
-        <v>1.06641779851202e-08</v>
+        <v>2.096796625217223e-10</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.709283381501336e-09</v>
+        <v>1.426918218999651e-11</v>
       </c>
       <c r="BR16" t="n">
-        <v>7.644210597845813e-09</v>
+        <v>7.580269745233181e-11</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.367775936955695e-08</v>
+        <v>6.473824254449312e-11</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.550177206714579e-09</v>
+        <v>4.535100073255194e-11</v>
       </c>
       <c r="BU16" t="n">
-        <v>6.810238595278406e-09</v>
+        <v>5.913131095880431e-11</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.645906295929763e-09</v>
+        <v>1.253500081510595e-10</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.548500216941306e-09</v>
+        <v>1.451385955864026e-10</v>
       </c>
       <c r="BX16" t="n">
-        <v>2.144331601172667e-09</v>
+        <v>5.371987576996418e-11</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.90798310484297e-09</v>
+        <v>1.011928943417395e-10</v>
       </c>
       <c r="BZ16" t="n">
-        <v>8.336642487449808e-09</v>
+        <v>1.141516742242388e-10</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.529723676848789e-09</v>
+        <v>1.402702398678457e-10</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.002003978735956e-09</v>
+        <v>8.633368325794422e-11</v>
       </c>
       <c r="CC16" t="n">
-        <v>6.625521020708902e-09</v>
+        <v>3.55693877129859e-11</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.709610727602012e-10</v>
+        <v>3.709390433703774e-12</v>
       </c>
       <c r="CE16" t="n">
-        <v>7.856387540527976e-09</v>
+        <v>5.440873446227457e-11</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.681534549964226e-09</v>
+        <v>1.807063700065559e-11</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.619042760443335e-09</v>
+        <v>1.083883954811071e-10</v>
       </c>
       <c r="CH16" t="n">
-        <v>2.273170984778972e-09</v>
+        <v>9.410757589867202e-11</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.907675351020544e-09</v>
+        <v>9.454801525032863e-11</v>
       </c>
       <c r="CJ16" t="n">
-        <v>9.084407670556516e-10</v>
+        <v>1.838640871498765e-11</v>
       </c>
       <c r="CK16" t="n">
-        <v>2.558347755865498e-09</v>
+        <v>1.450877785968974e-11</v>
       </c>
       <c r="CL16" t="n">
-        <v>3.877305143618059e-09</v>
+        <v>4.578808512900601e-11</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.095717916399508e-08</v>
+        <v>1.701729035463728e-10</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.04612238263735e-09</v>
+        <v>2.660974218748891e-10</v>
       </c>
       <c r="CO16" t="n">
-        <v>3.187642816371294e-09</v>
+        <v>1.709253988346759e-10</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.486161143622212e-08</v>
+        <v>4.367071287925128e-11</v>
       </c>
       <c r="CQ16" t="n">
-        <v>1.016779549445346e-08</v>
+        <v>7.979959054660313e-11</v>
       </c>
       <c r="CR16" t="n">
-        <v>7.259429501971226e-09</v>
+        <v>2.049178535190599e-11</v>
       </c>
       <c r="CS16" t="n">
-        <v>1.999710264044552e-08</v>
+        <v>1.692325724000909e-10</v>
       </c>
       <c r="CT16" t="n">
-        <v>1.527692461422703e-08</v>
+        <v>3.586320043019731e-12</v>
       </c>
       <c r="CU16" t="n">
-        <v>7.304757687620622e-09</v>
+        <v>1.795951061478451e-11</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.58127799743113e-09</v>
+        <v>7.458802672721809e-12</v>
       </c>
       <c r="CW16" t="n">
-        <v>4.954615828722808e-09</v>
+        <v>3.413518773198732e-11</v>
       </c>
       <c r="CX16" t="n">
-        <v>3.868027675935082e-09</v>
+        <v>4.960712830098801e-12</v>
       </c>
       <c r="CY16" t="n">
-        <v>6.602198787675206e-09</v>
+        <v>1.274055166922139e-10</v>
       </c>
       <c r="CZ16" t="n">
-        <v>3.764034417486073e-09</v>
+        <v>1.216521189340014e-10</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.532427600954179e-10</v>
+        <v>9.683844698349375e-11</v>
       </c>
       <c r="DB16" t="n">
-        <v>4.797413577506404e-09</v>
+        <v>2.117499925402555e-11</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.767590823182786e-09</v>
+        <v>1.631575430316445e-11</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.341330240795969e-09</v>
+        <v>5.289589946610995e-11</v>
       </c>
       <c r="DE16" t="n">
-        <v>9.660473310191264e-09</v>
+        <v>1.622310619175948e-10</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.421801343326479e-08</v>
+        <v>6.473752089952711e-11</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.250510178214427e-08</v>
+        <v>5.12597464474851e-11</v>
       </c>
       <c r="DH16" t="n">
-        <v>2.35117951774555e-08</v>
+        <v>1.380960762409345e-10</v>
       </c>
       <c r="DI16" t="n">
-        <v>3.100329948324543e-08</v>
+        <v>4.714563114904813e-11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4.148882126742137e-09</v>
+        <v>2.784616703888076e-10</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.436666145579693e-09</v>
+        <v>4.479310672378389e-11</v>
       </c>
       <c r="DL16" t="n">
-        <v>2.633818318997783e-08</v>
+        <v>2.916873687031085e-11</v>
       </c>
       <c r="DM16" t="n">
-        <v>5.069050956763022e-09</v>
+        <v>1.006662669889025e-10</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.006035255102233e-08</v>
+        <v>1.046033815121916e-10</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.569915696388648e-09</v>
+        <v>1.575890112848199e-10</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.359425234833907e-09</v>
+        <v>1.7790106193738e-11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>2.692886136301809e-09</v>
+        <v>3.082515145913511e-11</v>
       </c>
       <c r="DR16" t="n">
-        <v>4.011688314875528e-09</v>
+        <v>1.24955698566076e-10</v>
       </c>
       <c r="DS16" t="n">
-        <v>4.471569781117068e-09</v>
+        <v>4.784560941883953e-11</v>
       </c>
       <c r="DT16" t="n">
-        <v>1.819466466379538e-09</v>
+        <v>6.446698209983115e-12</v>
       </c>
       <c r="DU16" t="n">
-        <v>8.657748296059253e-09</v>
+        <v>1.769892704617249e-10</v>
       </c>
       <c r="DV16" t="n">
-        <v>1.57430246616741e-08</v>
+        <v>8.408133911341764e-11</v>
       </c>
       <c r="DW16" t="n">
-        <v>2.410374566608198e-09</v>
+        <v>6.348645220644045e-11</v>
       </c>
       <c r="DX16" t="n">
-        <v>4.379568707690851e-09</v>
+        <v>5.920432200046122e-11</v>
       </c>
       <c r="DY16" t="n">
-        <v>1.950817640761215e-08</v>
+        <v>1.128464682809138e-10</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.940123948278142e-10</v>
+        <v>1.303410573916253e-10</v>
       </c>
       <c r="EA16" t="n">
-        <v>1.449900466354848e-08</v>
+        <v>5.995980795203693e-11</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.493321022394412e-08</v>
+        <v>1.557942802543621e-10</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.367195106600661e-09</v>
+        <v>3.521856417609825e-11</v>
       </c>
       <c r="ED16" t="n">
-        <v>2.425865508470793e-09</v>
+        <v>8.939589346557142e-11</v>
       </c>
       <c r="EE16" t="n">
-        <v>6.007525032991623e-10</v>
+        <v>3.386457086973493e-11</v>
       </c>
       <c r="EF16" t="n">
-        <v>4.181536894520832e-09</v>
+        <v>4.204167222687794e-11</v>
       </c>
       <c r="EG16" t="n">
-        <v>2.296398848855574e-09</v>
+        <v>2.176580270185635e-11</v>
       </c>
       <c r="EH16" t="n">
-        <v>3.107123447421145e-09</v>
+        <v>3.195367581643183e-11</v>
       </c>
       <c r="EI16" t="n">
-        <v>5.140713632556526e-09</v>
+        <v>1.099377186508654e-10</v>
       </c>
       <c r="EJ16" t="n">
-        <v>7.314541861092039e-09</v>
+        <v>4.243692203198535e-11</v>
       </c>
       <c r="EK16" t="n">
-        <v>2.008015975718536e-09</v>
+        <v>1.150515377412731e-10</v>
       </c>
       <c r="EL16" t="n">
-        <v>6.49997389245982e-09</v>
+        <v>5.719958187655472e-11</v>
       </c>
       <c r="EM16" t="n">
-        <v>1.829704832090329e-09</v>
+        <v>5.521246220635545e-12</v>
       </c>
       <c r="EN16" t="n">
-        <v>6.058097579142441e-09</v>
+        <v>4.90640167383205e-11</v>
       </c>
       <c r="EO16" t="n">
-        <v>3.484829091959796e-09</v>
+        <v>5.8484328491204e-11</v>
       </c>
       <c r="EP16" t="n">
-        <v>3.375894452872785e-09</v>
+        <v>4.856436086608795e-11</v>
       </c>
       <c r="EQ16" t="n">
-        <v>5.516198609001322e-09</v>
+        <v>7.557951486880654e-11</v>
       </c>
       <c r="ER16" t="n">
-        <v>1.319616971251492e-09</v>
+        <v>1.165952057124997e-10</v>
       </c>
       <c r="ES16" t="n">
-        <v>4.751003146452604e-09</v>
+        <v>1.680168157380812e-12</v>
       </c>
       <c r="ET16" t="n">
-        <v>3.954386595950155e-09</v>
+        <v>1.430498774990241e-11</v>
       </c>
       <c r="EU16" t="n">
-        <v>2.853834057958693e-09</v>
+        <v>2.408130292397281e-11</v>
       </c>
       <c r="EV16" t="n">
-        <v>2.231507245653575e-08</v>
+        <v>7.117309519522053e-11</v>
       </c>
       <c r="EW16" t="n">
-        <v>1.366946733583063e-08</v>
+        <v>1.350172473824074e-10</v>
       </c>
       <c r="EX16" t="n">
-        <v>4.164191214073298e-10</v>
+        <v>2.076653952964858e-12</v>
       </c>
       <c r="EY16" t="n">
-        <v>4.654975960249885e-09</v>
+        <v>7.967156101518214e-11</v>
       </c>
       <c r="EZ16" t="n">
-        <v>2.1761450419433e-09</v>
+        <v>7.140709898378894e-12</v>
       </c>
       <c r="FA16" t="n">
-        <v>5.076011611038211e-09</v>
+        <v>1.141969990792191e-10</v>
       </c>
       <c r="FB16" t="n">
-        <v>2.817929889431525e-09</v>
+        <v>8.522039324221353e-11</v>
       </c>
       <c r="FC16" t="n">
-        <v>4.398367225988409e-10</v>
+        <v>1.013534811633576e-10</v>
       </c>
       <c r="FD16" t="n">
-        <v>2.119876496564643e-09</v>
+        <v>3.00748185036448e-12</v>
       </c>
       <c r="FE16" t="n">
-        <v>2.642281282660974e-09</v>
+        <v>3.866811731922937e-11</v>
       </c>
       <c r="FF16" t="n">
-        <v>3.103341361665457e-09</v>
+        <v>2.887701536224974e-11</v>
       </c>
       <c r="FG16" t="n">
-        <v>5.874666975103082e-09</v>
+        <v>6.759667825484428e-11</v>
       </c>
       <c r="FH16" t="n">
-        <v>1.039988184459162e-08</v>
+        <v>3.602244197375981e-11</v>
       </c>
       <c r="FI16" t="n">
-        <v>2.701771251167884e-08</v>
+        <v>1.077265568416585e-10</v>
       </c>
       <c r="FJ16" t="n">
-        <v>1.018449058420856e-08</v>
+        <v>2.005315358211135e-11</v>
       </c>
       <c r="FK16" t="n">
-        <v>1.444605590705805e-08</v>
+        <v>5.250060108874521e-11</v>
       </c>
       <c r="FL16" t="n">
-        <v>8.086523450856475e-09</v>
+        <v>3.236335158196546e-11</v>
       </c>
       <c r="FM16" t="n">
-        <v>3.030462547570778e-10</v>
+        <v>9.519171562111239e-11</v>
       </c>
       <c r="FN16" t="n">
-        <v>7.058729600828428e-09</v>
+        <v>9.538440176592999e-11</v>
       </c>
       <c r="FO16" t="n">
-        <v>9.933658340344209e-10</v>
+        <v>6.674385349958456e-11</v>
       </c>
       <c r="FP16" t="n">
-        <v>2.187473757686575e-09</v>
+        <v>1.25001120565571e-10</v>
       </c>
       <c r="FQ16" t="n">
-        <v>1.364542479009856e-09</v>
+        <v>1.080930830954507e-11</v>
       </c>
       <c r="FR16" t="n">
-        <v>1.231353019548465e-09</v>
+        <v>2.239807228576751e-10</v>
       </c>
       <c r="FS16" t="n">
-        <v>2.986279667993585e-09</v>
+        <v>9.305649306678987e-11</v>
       </c>
       <c r="FT16" t="n">
-        <v>1.249522263435665e-08</v>
+        <v>1.856503839547941e-10</v>
       </c>
       <c r="FU16" t="n">
-        <v>4.856917090734214e-09</v>
+        <v>7.675535901308095e-11</v>
       </c>
       <c r="FV16" t="n">
-        <v>1.679213212923969e-08</v>
+        <v>2.878586813359618e-10</v>
       </c>
       <c r="FW16" t="n">
-        <v>2.567366319539133e-09</v>
+        <v>1.721618680949888e-10</v>
       </c>
       <c r="FX16" t="n">
-        <v>5.423366200574264e-10</v>
+        <v>1.015337397491933e-10</v>
       </c>
       <c r="FY16" t="n">
-        <v>7.948231406373907e-09</v>
+        <v>2.311392049980654e-11</v>
       </c>
       <c r="FZ16" t="n">
-        <v>1.285581507914912e-08</v>
+        <v>1.323338244541006e-10</v>
       </c>
       <c r="GA16" t="n">
-        <v>2.450952552024432e-09</v>
+        <v>1.46371706422066e-10</v>
       </c>
       <c r="GB16" t="n">
-        <v>2.087377382054001e-09</v>
+        <v>5.947213554957642e-11</v>
       </c>
       <c r="GC16" t="n">
-        <v>6.383314765656678e-09</v>
+        <v>9.248158489016944e-11</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.463381771316108e-08</v>
+        <v>2.562895728974723e-10</v>
       </c>
       <c r="GE16" t="n">
-        <v>3.953358174157984e-08</v>
+        <v>1.002678981509852e-10</v>
       </c>
       <c r="GF16" t="n">
-        <v>4.330169556254759e-09</v>
+        <v>2.813105651200409e-12</v>
       </c>
       <c r="GG16" t="n">
-        <v>2.032256674056043e-08</v>
+        <v>5.185382678796202e-11</v>
       </c>
     </row>
   </sheetData>
